--- a/results_gen/outputs/Test_all.xlsx
+++ b/results_gen/outputs/Test_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reube\Parallel-Monte-Carlo-Tree-Search-For-The-Orienteering-Problem\results_gen\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D31F10F-A87D-4CC8-A9CC-DE6804EBE546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5351F0F-73B9-4227-89EA-B500E874AF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-45" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{260B2045-1352-43BA-9B1E-29C2A8BE3BD5}"/>
+    <workbookView xWindow="-38520" yWindow="-45" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{260B2045-1352-43BA-9B1E-29C2A8BE3BD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Test1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="41">
   <si>
     <t>raw_reward</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>OR-Tools</t>
-  </si>
-  <si>
-    <t>Simple_WU</t>
   </si>
   <si>
     <t>Tree</t>
@@ -122,9 +119,6 @@
     <t>OR wins with the larger budget</t>
   </si>
   <si>
-    <t>MCTS does worse comparied to OR with lareger bugets, further testing larger budgets</t>
-  </si>
-  <si>
     <t>Shows that with smaller number of workers tree is doing better then Wu probel due to the diveed of E and S workers</t>
   </si>
   <si>
@@ -174,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +217,11 @@
       <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -339,18 +338,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -359,7 +352,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -368,18 +380,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -391,14 +395,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -733,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2055FE3-E712-4367-9B42-B5E3B258A2F1}">
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.5703125" customWidth="1"/>
@@ -741,41 +743,41 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
@@ -849,13 +851,13 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>14</v>
+      <c r="A6" s="15" t="s">
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>376</v>
       </c>
       <c r="E6">
@@ -866,9 +868,9 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>384.4</v>
@@ -879,14 +881,14 @@
       <c r="E7">
         <v>376</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>366.2</v>
@@ -902,9 +904,9 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>349.6</v>
@@ -920,31 +922,31 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="6">
+        <v>12</v>
+      </c>
+      <c r="C10" s="4">
         <v>390.2</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="10">
         <v>5.2630789467763091</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>384</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="6">
         <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>558</v>
       </c>
       <c r="E11">
@@ -957,9 +959,9 @@
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="6">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4">
         <v>508.4</v>
       </c>
       <c r="D12">
@@ -975,7 +977,7 @@
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>491.8</v>
@@ -993,7 +995,7 @@
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>487.4</v>
@@ -1011,7 +1013,7 @@
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>491.33333333333331</v>
@@ -1027,13 +1029,13 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>16</v>
+      <c r="A16" s="22" t="s">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>315</v>
       </c>
       <c r="E16">
@@ -1044,11 +1046,11 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4">
         <v>337.6</v>
       </c>
       <c r="D17">
@@ -1057,14 +1059,14 @@
       <c r="E17">
         <v>310</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="6">
         <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
+      <c r="A18" s="22"/>
       <c r="B18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <v>316.39999999999998</v>
@@ -1080,52 +1082,52 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>320</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="10">
         <v>22.660538387249321</v>
       </c>
       <c r="E19">
         <v>290</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>348</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20">
         <v>320.2</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="10">
         <v>22.12916627439904</v>
       </c>
       <c r="E20">
         <v>293</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="6">
         <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>15</v>
+      <c r="A21" s="22" t="s">
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>444</v>
       </c>
       <c r="E21">
@@ -1136,14 +1138,14 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4">
         <v>446.8</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="10">
         <v>32.221111091953368</v>
       </c>
       <c r="E22">
@@ -1154,9 +1156,9 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>418.6</v>
@@ -1172,29 +1174,29 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
+      <c r="A24" s="22"/>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>406.4</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="10">
         <v>28.605943438383569</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="6">
         <v>383</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="6">
         <v>454</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5">
+        <v>12</v>
+      </c>
+      <c r="C25" s="3">
         <v>430.8</v>
       </c>
       <c r="D25">
@@ -1208,13 +1210,13 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>18</v>
+      <c r="A26" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="7">
         <v>453</v>
       </c>
       <c r="E26">
@@ -1225,11 +1227,11 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
+        <v>9</v>
+      </c>
+      <c r="C27" s="4">
         <v>473.6</v>
       </c>
       <c r="D27">
@@ -1238,14 +1240,14 @@
       <c r="E27">
         <v>462</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="6">
         <v>486</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>449.2</v>
@@ -1256,17 +1258,17 @@
       <c r="E28">
         <v>431</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="6">
         <v>478</v>
       </c>
       <c r="H28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29">
         <v>444</v>
@@ -1277,16 +1279,16 @@
       <c r="E29">
         <v>426</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="6">
         <v>465</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="5">
+        <v>12</v>
+      </c>
+      <c r="C30" s="3">
         <v>465.2</v>
       </c>
       <c r="D30">
@@ -1295,18 +1297,18 @@
       <c r="E30">
         <v>445</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="7">
         <v>622</v>
       </c>
       <c r="E31">
@@ -1319,30 +1321,30 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32">
         <v>601.79999999999995</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="10">
         <v>30.15294347157506</v>
       </c>
       <c r="E32">
         <v>573</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="4">
         <v>643</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>570</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="10">
         <v>24.969981978367549</v>
       </c>
       <c r="E33">
@@ -1355,12 +1357,12 @@
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>567.4</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="10">
         <v>26.6608326951729</v>
       </c>
       <c r="E34">
@@ -1373,29 +1375,29 @@
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="5">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3">
         <v>611.20000000000005</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="10">
         <v>26.17632518135424</v>
       </c>
       <c r="E35">
         <v>589</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="4">
         <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="7">
         <v>414</v>
       </c>
       <c r="E36">
@@ -1408,7 +1410,7 @@
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37">
         <v>338.6</v>
@@ -1426,7 +1428,7 @@
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38">
         <v>345.6</v>
@@ -1444,7 +1446,7 @@
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39">
         <v>321</v>
@@ -1462,7 +1464,7 @@
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40">
         <v>308</v>
@@ -1479,12 +1481,12 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="7">
         <v>536</v>
       </c>
       <c r="E41">
@@ -1497,7 +1499,7 @@
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>474.2</v>
@@ -1515,7 +1517,7 @@
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43">
         <v>458.6</v>
@@ -1533,12 +1535,12 @@
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44">
         <v>420.8</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="12">
         <v>47.66235411726953</v>
       </c>
       <c r="E44">
@@ -1551,12 +1553,12 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45">
         <v>449.25</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="12">
         <v>61.451200151014127</v>
       </c>
       <c r="E45">
@@ -1567,8 +1569,8 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>24</v>
+      <c r="A46" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>8</v>
@@ -1603,351 +1605,481 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="18"/>
-      <c r="B47" s="1" t="s">
-        <v>11</v>
+      <c r="B47" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="C47">
-        <v>342.4</v>
+        <v>350.2</v>
       </c>
       <c r="D47">
-        <v>24.398770460824451</v>
+        <v>9.4180677423768842</v>
       </c>
       <c r="E47">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="F47">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G47">
-        <v>0.46023111343383788</v>
+        <v>1.1950191020965579</v>
       </c>
       <c r="H47">
-        <v>2.6846504271177369E-2</v>
+        <v>0.18039257824792401</v>
       </c>
       <c r="I47">
-        <v>0.43242383003234858</v>
+        <v>1.022696733474731</v>
       </c>
       <c r="J47">
-        <v>0.49813580513000488</v>
+        <v>1.462550163269043</v>
       </c>
       <c r="K47">
-        <v>98.911688245431449</v>
+        <v>98.749927787351922</v>
       </c>
       <c r="L47">
-        <v>0.4055898439879066</v>
+        <v>0.51153148288347228</v>
       </c>
       <c r="M47">
         <v>98.521163953680173</v>
       </c>
       <c r="N47">
-        <v>99.329966244077795</v>
+        <v>99.66498312203889</v>
+      </c>
+      <c r="O47">
+        <v>4613.8</v>
+      </c>
+      <c r="P47">
+        <v>4718.344010349394</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>9742</v>
+      </c>
+      <c r="S47">
+        <v>0.46138000000000001</v>
+      </c>
+      <c r="T47">
+        <v>0.47183440103493929</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0.97419999999999995</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="18"/>
       <c r="B48" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>348.4</v>
+        <v>342.4</v>
       </c>
       <c r="D48">
-        <v>11.696153213770771</v>
+        <v>24.398770460824451</v>
       </c>
       <c r="E48">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="F48">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G48">
-        <v>1.896955394744873</v>
+        <v>0.46023111343383788</v>
       </c>
       <c r="H48">
-        <v>0.22758657751800609</v>
+        <v>2.6846504271177369E-2</v>
       </c>
       <c r="I48">
-        <v>1.507538795471191</v>
+        <v>0.43242383003234858</v>
       </c>
       <c r="J48">
-        <v>2.0896544456481929</v>
+        <v>0.49813580513000488</v>
       </c>
       <c r="K48">
-        <v>99.396969619670017</v>
+        <v>98.911688245431449</v>
       </c>
       <c r="L48">
-        <v>0.14982410254615131</v>
+        <v>0.4055898439879066</v>
       </c>
       <c r="M48">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N48">
         <v>99.329966244077795</v>
-      </c>
-      <c r="N48">
-        <v>99.66498312203889</v>
-      </c>
-      <c r="O48">
-        <v>2947.6</v>
-      </c>
-      <c r="P48">
-        <v>2418.0015095115218</v>
-      </c>
-      <c r="Q48">
-        <v>223</v>
-      </c>
-      <c r="R48">
-        <v>5472</v>
-      </c>
-      <c r="S48">
-        <v>0.29476000000000002</v>
-      </c>
-      <c r="T48">
-        <v>0.2418001509511522</v>
-      </c>
-      <c r="U48">
-        <v>2.23E-2</v>
-      </c>
-      <c r="V48">
-        <v>0.54720000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="19"/>
       <c r="B49" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>359</v>
+        <v>11</v>
+      </c>
+      <c r="C49">
+        <v>348.4</v>
       </c>
       <c r="D49">
-        <v>14.071247279470301</v>
+        <v>11.696153213770771</v>
       </c>
       <c r="E49">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F49">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G49">
-        <v>2.0801680564880369</v>
+        <v>1.896955394744873</v>
       </c>
       <c r="H49">
-        <v>8.8585796560101085E-2</v>
+        <v>0.22758657751800609</v>
       </c>
       <c r="I49">
-        <v>1.922396183013916</v>
+        <v>1.507538795471191</v>
       </c>
       <c r="J49">
-        <v>2.1307270526885991</v>
+        <v>2.0896544456481929</v>
       </c>
       <c r="K49">
-        <v>99.369215912774933</v>
+        <v>99.396969619670017</v>
       </c>
       <c r="L49">
-        <v>0.49577398783232568</v>
+        <v>0.14982410254615131</v>
       </c>
       <c r="M49">
-        <v>98.521163953680173</v>
+        <v>99.329966244077795</v>
       </c>
       <c r="N49">
         <v>99.66498312203889</v>
       </c>
+      <c r="O49">
+        <v>2947.6</v>
+      </c>
+      <c r="P49">
+        <v>2418.0015095115218</v>
+      </c>
+      <c r="Q49">
+        <v>223</v>
+      </c>
+      <c r="R49">
+        <v>5472</v>
+      </c>
+      <c r="S49">
+        <v>0.29476000000000002</v>
+      </c>
+      <c r="T49">
+        <v>0.2418001509511522</v>
+      </c>
+      <c r="U49">
+        <v>2.23E-2</v>
+      </c>
+      <c r="V49">
+        <v>0.54720000000000002</v>
+      </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>30</v>
+      <c r="A50" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="4">
+        <v>359</v>
+      </c>
+      <c r="D50">
+        <v>14.071247279470301</v>
+      </c>
+      <c r="E50">
+        <v>343</v>
+      </c>
+      <c r="F50">
+        <v>377</v>
+      </c>
+      <c r="G50">
+        <v>2.0801680564880369</v>
+      </c>
+      <c r="H50">
+        <v>8.8585796560101085E-2</v>
+      </c>
+      <c r="I50">
+        <v>1.922396183013916</v>
+      </c>
+      <c r="J50">
+        <v>2.1307270526885991</v>
+      </c>
+      <c r="K50">
+        <v>99.369215912774933</v>
+      </c>
+      <c r="L50">
+        <v>0.49577398783232568</v>
+      </c>
+      <c r="M50">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N50">
+        <v>99.66498312203889</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="20"/>
+      <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>348</v>
       </c>
-      <c r="E50">
+      <c r="E51">
         <v>348</v>
       </c>
-      <c r="F50">
+      <c r="F51">
         <v>348</v>
       </c>
-      <c r="G50">
+      <c r="G51">
         <v>2.0099177360534668</v>
       </c>
-      <c r="I50">
+      <c r="I51">
         <v>2.0099177360534668</v>
       </c>
-      <c r="J50">
+      <c r="J51">
         <v>2.0099177360534668</v>
       </c>
-      <c r="K50">
+      <c r="K51">
         <v>100</v>
       </c>
-      <c r="M50">
+      <c r="M51">
         <v>100</v>
       </c>
-      <c r="N50">
+      <c r="N51">
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51">
-        <v>417.8</v>
-      </c>
-      <c r="D51">
-        <v>11.122050170719421</v>
-      </c>
-      <c r="E51">
-        <v>405</v>
-      </c>
-      <c r="F51">
-        <v>434</v>
-      </c>
-      <c r="G51">
-        <v>0.59997572898864748</v>
-      </c>
-      <c r="H51">
-        <v>5.799737114957286E-2</v>
-      </c>
-      <c r="I51">
-        <v>0.55214214324951172</v>
-      </c>
-      <c r="J51">
-        <v>0.68944382667541504</v>
-      </c>
-      <c r="K51">
-        <v>99.376154339498697</v>
-      </c>
-      <c r="L51">
-        <v>0.27128053525298179</v>
-      </c>
-      <c r="M51">
-        <v>98.890872965260129</v>
-      </c>
-      <c r="N51">
-        <v>99.497474683058343</v>
-      </c>
-    </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
-      <c r="B52" s="1" t="s">
-        <v>12</v>
+      <c r="A52" s="20"/>
+      <c r="B52" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="C52">
-        <v>445.2</v>
+        <v>443.6</v>
       </c>
       <c r="D52">
-        <v>17.68332547910601</v>
+        <v>10.212737145349429</v>
       </c>
       <c r="E52">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F52">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G52">
-        <v>2.6020132064819341</v>
+        <v>1.564440631866455</v>
       </c>
       <c r="H52">
-        <v>0.16470903347987501</v>
+        <v>0.1698978432962</v>
       </c>
       <c r="I52">
-        <v>2.4085583686828609</v>
+        <v>1.391818761825562</v>
       </c>
       <c r="J52">
-        <v>2.7934713363647461</v>
+        <v>1.7636628150939939</v>
       </c>
       <c r="K52">
-        <v>99.376154339498683</v>
+        <v>99.497474683058329</v>
       </c>
       <c r="L52">
-        <v>0.27128053525298979</v>
+        <v>1.5888218580782551E-14</v>
       </c>
       <c r="M52">
-        <v>98.890872965260115</v>
+        <v>99.497474683058314</v>
       </c>
       <c r="N52">
         <v>99.497474683058343</v>
       </c>
       <c r="O52">
+        <v>3729.2</v>
+      </c>
+      <c r="P52">
+        <v>5118.9370673998328</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>9829</v>
+      </c>
+      <c r="S52">
+        <v>0.37291999999999997</v>
+      </c>
+      <c r="T52">
+        <v>0.51189370673998325</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0.9829</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="21"/>
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53">
+        <v>417.8</v>
+      </c>
+      <c r="D53">
+        <v>11.122050170719421</v>
+      </c>
+      <c r="E53">
+        <v>405</v>
+      </c>
+      <c r="F53">
+        <v>434</v>
+      </c>
+      <c r="G53">
+        <v>0.59997572898864748</v>
+      </c>
+      <c r="H53">
+        <v>5.799737114957286E-2</v>
+      </c>
+      <c r="I53">
+        <v>0.55214214324951172</v>
+      </c>
+      <c r="J53">
+        <v>0.68944382667541504</v>
+      </c>
+      <c r="K53">
+        <v>99.376154339498697</v>
+      </c>
+      <c r="L53">
+        <v>0.27128053525298179</v>
+      </c>
+      <c r="M53">
+        <v>98.890872965260129</v>
+      </c>
+      <c r="N53">
+        <v>99.497474683058343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>445.2</v>
+      </c>
+      <c r="D54">
+        <v>17.68332547910601</v>
+      </c>
+      <c r="E54">
+        <v>428</v>
+      </c>
+      <c r="F54">
+        <v>466</v>
+      </c>
+      <c r="G54">
+        <v>2.6020132064819341</v>
+      </c>
+      <c r="H54">
+        <v>0.16470903347987501</v>
+      </c>
+      <c r="I54">
+        <v>2.4085583686828609</v>
+      </c>
+      <c r="J54">
+        <v>2.7934713363647461</v>
+      </c>
+      <c r="K54">
+        <v>99.376154339498683</v>
+      </c>
+      <c r="L54">
+        <v>0.27128053525298979</v>
+      </c>
+      <c r="M54">
+        <v>98.890872965260115</v>
+      </c>
+      <c r="N54">
+        <v>99.497474683058343</v>
+      </c>
+      <c r="O54">
         <v>5952.8</v>
       </c>
-      <c r="P52">
+      <c r="P54">
         <v>657.89908040671401</v>
       </c>
-      <c r="Q52">
+      <c r="Q54">
         <v>5226</v>
       </c>
-      <c r="R52">
+      <c r="R54">
         <v>6961</v>
       </c>
-      <c r="S52">
+      <c r="S54">
         <v>0.59528000000000003</v>
       </c>
-      <c r="T52">
+      <c r="T54">
         <v>6.5789908040671363E-2</v>
       </c>
-      <c r="U52">
+      <c r="U54">
         <v>0.52259999999999995</v>
       </c>
-      <c r="V52">
+      <c r="V54">
         <v>0.69609999999999994</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
-      <c r="B53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="6">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="4">
         <v>440.8</v>
       </c>
-      <c r="D53">
+      <c r="D55">
         <v>18.61988184710096</v>
       </c>
-      <c r="E53">
+      <c r="E55">
         <v>414</v>
       </c>
-      <c r="F53">
+      <c r="F55">
         <v>460</v>
       </c>
-      <c r="G53">
+      <c r="G55">
         <v>2.5720071315765378</v>
       </c>
-      <c r="H53">
+      <c r="H55">
         <v>6.8143471532315286E-2</v>
       </c>
-      <c r="I53">
+      <c r="I55">
         <v>2.4639968872070308</v>
       </c>
-      <c r="J53">
+      <c r="J55">
         <v>2.6415882110595699</v>
       </c>
-      <c r="K53">
+      <c r="K55">
         <v>99.426406871192867</v>
       </c>
-      <c r="L53">
+      <c r="L55">
         <v>0.3185299821684201</v>
       </c>
-      <c r="M53">
+      <c r="M55">
         <v>98.890872965260115</v>
       </c>
-      <c r="N53">
+      <c r="N55">
         <v>99.748737341529164</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A53"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="O3:R3"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="A26:A30"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A11:A15"/>
@@ -1960,7 +2092,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B9F7C1-6CD3-4B61-9368-31485E040906}">
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
@@ -1974,36 +2106,36 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
@@ -2077,13 +2209,13 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>14</v>
+      <c r="A6" s="15" t="s">
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>376</v>
       </c>
       <c r="E6">
@@ -2094,1268 +2226,1211 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>379.2</v>
+      </c>
+      <c r="D7">
+        <v>23.847431727546681</v>
+      </c>
+      <c r="E7">
+        <v>343</v>
+      </c>
+      <c r="F7">
+        <v>402</v>
+      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C8">
-        <v>379.2</v>
+        <v>357.6</v>
       </c>
       <c r="D8">
-        <v>23.847431727546681</v>
+        <v>14.0107101889947</v>
       </c>
       <c r="E8">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F8">
-        <v>402</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9">
-        <v>357.6</v>
+        <v>376.8</v>
       </c>
       <c r="D9">
-        <v>14.0107101889947</v>
+        <v>23.805461558222309</v>
       </c>
       <c r="E9">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F9">
-        <v>379</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="15"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C10">
-        <v>376.8</v>
+      <c r="C10" s="4">
+        <v>395.8</v>
       </c>
       <c r="D10">
-        <v>23.805461558222309</v>
+        <v>10.497618777608571</v>
       </c>
       <c r="E10">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="F10">
-        <v>417</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
+      <c r="A11" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="6">
-        <v>395.8</v>
-      </c>
-      <c r="D11">
-        <v>10.497618777608571</v>
+        <v>8</v>
+      </c>
+      <c r="C11" s="7">
+        <v>558</v>
       </c>
       <c r="E11">
-        <v>378</v>
-      </c>
-      <c r="F11">
-        <v>404</v>
+        <v>558</v>
+      </c>
+      <c r="F11" s="11">
+        <v>558</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>524.79999999999995</v>
+      </c>
+      <c r="D12">
+        <v>6.4187226143524772</v>
+      </c>
+      <c r="E12">
+        <v>514</v>
+      </c>
+      <c r="F12">
+        <v>530</v>
+      </c>
+      <c r="H12" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="9">
-        <v>558</v>
-      </c>
-      <c r="E12">
-        <v>558</v>
-      </c>
-      <c r="F12" s="17">
-        <v>558</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>485.6</v>
+        <v>489.2</v>
       </c>
       <c r="D13">
-        <v>8.4439327330338116</v>
+        <v>9.7826376811164799</v>
       </c>
       <c r="E13">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F13">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>524.79999999999995</v>
+        <v>487.8</v>
       </c>
       <c r="D14">
-        <v>6.4187226143524772</v>
+        <v>2.8635642126552661</v>
       </c>
       <c r="E14">
-        <v>514</v>
+        <v>484</v>
       </c>
       <c r="F14">
-        <v>530</v>
-      </c>
-      <c r="H14" t="s">
-        <v>26</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>498.4</v>
+      </c>
+      <c r="D15">
+        <v>13.520355024924459</v>
+      </c>
+      <c r="E15">
+        <v>480</v>
+      </c>
+      <c r="F15">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2">
+        <v>315</v>
+      </c>
+      <c r="E16">
+        <v>315</v>
+      </c>
+      <c r="F16">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4">
+        <v>345.4</v>
+      </c>
+      <c r="D17">
+        <v>4.1593268686170903</v>
+      </c>
+      <c r="E17">
+        <v>341</v>
+      </c>
+      <c r="F17" s="6">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>328</v>
+      </c>
+      <c r="D18">
+        <v>21.095023109728981</v>
+      </c>
+      <c r="E18">
+        <v>296</v>
+      </c>
+      <c r="F18">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C15">
-        <v>489.2</v>
-      </c>
-      <c r="D15">
-        <v>9.7826376811164799</v>
-      </c>
-      <c r="E15">
-        <v>478</v>
-      </c>
-      <c r="F15">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="1" t="s">
+      <c r="C19">
+        <v>320.60000000000002</v>
+      </c>
+      <c r="D19">
+        <v>12.218837915284739</v>
+      </c>
+      <c r="E19">
+        <v>306</v>
+      </c>
+      <c r="F19">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="26"/>
+      <c r="B20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C16">
-        <v>487.8</v>
-      </c>
-      <c r="D16">
-        <v>2.8635642126552661</v>
-      </c>
-      <c r="E16">
-        <v>484</v>
-      </c>
-      <c r="F16">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17">
-        <v>498.4</v>
-      </c>
-      <c r="D17">
-        <v>13.520355024924459</v>
-      </c>
-      <c r="E17">
+      <c r="C20">
+        <v>334.2</v>
+      </c>
+      <c r="D20">
+        <v>11.0770032048384</v>
+      </c>
+      <c r="E20">
+        <v>317</v>
+      </c>
+      <c r="F20">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>444</v>
+      </c>
+      <c r="E21">
+        <v>444</v>
+      </c>
+      <c r="F21">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>413</v>
+      </c>
+      <c r="D22">
+        <v>19.013153341831551</v>
+      </c>
+      <c r="E22">
+        <v>387</v>
+      </c>
+      <c r="F22">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>424.2</v>
+      </c>
+      <c r="D23">
+        <v>24.48877293781786</v>
+      </c>
+      <c r="E23">
+        <v>403</v>
+      </c>
+      <c r="F23">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>403.4</v>
+      </c>
+      <c r="D24">
+        <v>10.968135666557</v>
+      </c>
+      <c r="E24">
+        <v>387</v>
+      </c>
+      <c r="F24">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
+      <c r="B25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="4">
+        <v>452.2</v>
+      </c>
+      <c r="D25">
+        <v>24.488772937817849</v>
+      </c>
+      <c r="E25">
+        <v>417</v>
+      </c>
+      <c r="F25" s="4">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5">
+        <v>453</v>
+      </c>
+      <c r="E26">
+        <v>453</v>
+      </c>
+      <c r="F26">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="20"/>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>453.8</v>
+      </c>
+      <c r="D27">
+        <v>20.620378270051209</v>
+      </c>
+      <c r="E27">
+        <v>427</v>
+      </c>
+      <c r="F27">
         <v>480</v>
       </c>
-      <c r="F17">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="H27" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="20"/>
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>455.4</v>
+      </c>
+      <c r="D28">
+        <v>23.028243528328431</v>
+      </c>
+      <c r="E28">
+        <v>435</v>
+      </c>
+      <c r="F28">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
+      <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29">
+        <v>465.4</v>
+      </c>
+      <c r="D29">
+        <v>30.38585197094201</v>
+      </c>
+      <c r="E29">
+        <v>427</v>
+      </c>
+      <c r="F29">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="4">
+        <v>486.8</v>
+      </c>
+      <c r="D30">
+        <v>14.04279174523357</v>
+      </c>
+      <c r="E30">
+        <v>476</v>
+      </c>
+      <c r="F30">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="3">
-        <v>315</v>
-      </c>
-      <c r="E18">
-        <v>315</v>
-      </c>
-      <c r="F18">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="1" t="s">
+      <c r="C31" s="5">
+        <v>622</v>
+      </c>
+      <c r="E31">
+        <v>622</v>
+      </c>
+      <c r="F31">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32">
+        <v>589.6</v>
+      </c>
+      <c r="D32">
+        <v>17.00882124075622</v>
+      </c>
+      <c r="E32">
+        <v>571</v>
+      </c>
+      <c r="F32">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="6">
-        <v>345.4</v>
-      </c>
-      <c r="D20">
-        <v>4.1593268686170903</v>
-      </c>
-      <c r="E20">
-        <v>341</v>
-      </c>
-      <c r="F20" s="8">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="1" t="s">
+      <c r="C33">
+        <v>576.6</v>
+      </c>
+      <c r="D33">
+        <v>22.578751072634649</v>
+      </c>
+      <c r="E33">
+        <v>559</v>
+      </c>
+      <c r="F33">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+      <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C21">
-        <v>328</v>
-      </c>
-      <c r="D21">
-        <v>21.095023109728981</v>
-      </c>
-      <c r="E21">
-        <v>296</v>
-      </c>
-      <c r="F21">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="1" t="s">
+      <c r="C34">
+        <v>580.4</v>
+      </c>
+      <c r="D34">
+        <v>30.154601638887559</v>
+      </c>
+      <c r="E34">
+        <v>542</v>
+      </c>
+      <c r="F34">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" s="25"/>
+      <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C22">
-        <v>320.60000000000002</v>
-      </c>
-      <c r="D22">
-        <v>12.218837915284739</v>
-      </c>
-      <c r="E22">
-        <v>306</v>
-      </c>
-      <c r="F22">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="25"/>
-      <c r="B23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23">
-        <v>334.2</v>
-      </c>
-      <c r="D23">
-        <v>11.0770032048384</v>
-      </c>
-      <c r="E23">
-        <v>317</v>
-      </c>
-      <c r="F23">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>444</v>
-      </c>
-      <c r="E24">
-        <v>444</v>
-      </c>
-      <c r="F24">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="1"/>
-      <c r="I25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26">
-        <v>413</v>
-      </c>
-      <c r="D26">
-        <v>19.013153341831551</v>
-      </c>
-      <c r="E26">
-        <v>387</v>
-      </c>
-      <c r="F26">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27">
-        <v>424.2</v>
-      </c>
-      <c r="D27">
-        <v>24.48877293781786</v>
-      </c>
-      <c r="E27">
-        <v>403</v>
-      </c>
-      <c r="F27">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28">
-        <v>403.4</v>
-      </c>
-      <c r="D28">
-        <v>10.968135666557</v>
-      </c>
-      <c r="E28">
-        <v>387</v>
-      </c>
-      <c r="F28">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="6">
-        <v>452.2</v>
-      </c>
-      <c r="D29">
-        <v>24.488772937817849</v>
-      </c>
-      <c r="E29">
-        <v>417</v>
-      </c>
-      <c r="F29" s="6">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="7">
-        <v>453</v>
-      </c>
-      <c r="E30">
-        <v>453</v>
-      </c>
-      <c r="F30">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32">
-        <v>453.8</v>
-      </c>
-      <c r="D32">
-        <v>20.620378270051209</v>
-      </c>
-      <c r="E32">
-        <v>427</v>
-      </c>
-      <c r="F32">
-        <v>480</v>
-      </c>
-      <c r="H32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33">
-        <v>455.4</v>
-      </c>
-      <c r="D33">
-        <v>23.028243528328431</v>
-      </c>
-      <c r="E33">
-        <v>435</v>
-      </c>
-      <c r="F33">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34">
-        <v>465.4</v>
-      </c>
-      <c r="D34">
-        <v>30.38585197094201</v>
-      </c>
-      <c r="E34">
-        <v>427</v>
-      </c>
-      <c r="F34">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="6">
-        <v>486.8</v>
+      <c r="C35">
+        <v>592</v>
       </c>
       <c r="D35">
-        <v>14.04279174523357</v>
+        <v>37.993420483025737</v>
       </c>
       <c r="E35">
-        <v>476</v>
+        <v>559</v>
       </c>
       <c r="F35">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="20" t="s">
-        <v>19</v>
+        <v>643</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="7">
-        <v>622</v>
+        <v>414</v>
       </c>
       <c r="E36">
-        <v>622</v>
+        <v>414</v>
       </c>
       <c r="F36">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37">
+        <v>355.8</v>
+      </c>
+      <c r="D37">
+        <v>47.060599231204023</v>
+      </c>
+      <c r="E37">
+        <v>273</v>
+      </c>
+      <c r="F37">
+        <v>383</v>
+      </c>
+      <c r="H37" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>589.6</v>
+        <v>303.60000000000002</v>
       </c>
       <c r="D38">
-        <v>17.00882124075622</v>
+        <v>33.738701812606827</v>
       </c>
       <c r="E38">
-        <v>571</v>
+        <v>272</v>
       </c>
       <c r="F38">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C39">
-        <v>576.6</v>
+      <c r="C39" s="3">
+        <v>341.6</v>
       </c>
       <c r="D39">
-        <v>22.578751072634649</v>
+        <v>40.457384987168901</v>
       </c>
       <c r="E39">
-        <v>559</v>
+        <v>275</v>
       </c>
       <c r="F39">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" s="25"/>
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C40">
-        <v>580.4</v>
+      <c r="C40" s="13">
+        <v>296.2</v>
       </c>
       <c r="D40">
-        <v>30.154601638887559</v>
+        <v>15.6588633048507</v>
       </c>
       <c r="E40">
-        <v>542</v>
+        <v>271</v>
       </c>
       <c r="F40">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="22"/>
+        <v>309</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
+        <v>21</v>
+      </c>
       <c r="B41" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41">
-        <v>592</v>
-      </c>
-      <c r="D41">
-        <v>37.993420483025737</v>
+        <v>8</v>
+      </c>
+      <c r="C41" s="7">
+        <v>536</v>
       </c>
       <c r="E41">
-        <v>559</v>
+        <v>536</v>
       </c>
       <c r="F41">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
-        <v>21</v>
-      </c>
+        <v>536</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
       <c r="B42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>453</v>
+      </c>
+      <c r="D42">
+        <v>43.550736694878843</v>
+      </c>
+      <c r="E42">
+        <v>396</v>
+      </c>
+      <c r="F42">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43">
+        <v>440.6</v>
+      </c>
+      <c r="D43">
+        <v>49.505555243830969</v>
+      </c>
+      <c r="E43">
+        <v>362</v>
+      </c>
+      <c r="F43">
+        <v>484</v>
+      </c>
+      <c r="H43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44">
+        <v>374.2</v>
+      </c>
+      <c r="D44">
+        <v>39.079406341447921</v>
+      </c>
+      <c r="E44">
+        <v>338</v>
+      </c>
+      <c r="F44">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" s="25"/>
+      <c r="B45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="13">
+        <v>396.75</v>
+      </c>
+      <c r="D45">
+        <v>41.772199686713492</v>
+      </c>
+      <c r="E45">
+        <v>354</v>
+      </c>
+      <c r="F45">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="9">
-        <v>414</v>
-      </c>
-      <c r="E42">
-        <v>414</v>
-      </c>
-      <c r="F42">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
-      <c r="B44" s="1" t="s">
+      <c r="C46" s="5">
+        <v>303</v>
+      </c>
+      <c r="E46">
+        <v>303</v>
+      </c>
+      <c r="F46">
+        <v>303</v>
+      </c>
+      <c r="G46">
+        <v>2.050655841827393</v>
+      </c>
+      <c r="I46">
+        <v>2.050655841827393</v>
+      </c>
+      <c r="J46">
+        <v>2.050655841827393</v>
+      </c>
+      <c r="K46">
+        <v>99.621165057908925</v>
+      </c>
+      <c r="M46">
+        <v>99.621165057908925</v>
+      </c>
+      <c r="N46">
+        <v>99.621165057908925</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="20"/>
+      <c r="B47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <v>352.2</v>
+      </c>
+      <c r="D47">
+        <v>13.367871932360821</v>
+      </c>
+      <c r="E47">
+        <v>339</v>
+      </c>
+      <c r="F47">
+        <v>372</v>
+      </c>
+      <c r="G47">
+        <v>1.299343872070313</v>
+      </c>
+      <c r="H47">
+        <v>0.23668983572394969</v>
+      </c>
+      <c r="I47">
+        <v>1.0473401546478269</v>
+      </c>
+      <c r="J47">
+        <v>1.566922664642334</v>
+      </c>
+      <c r="K47">
+        <v>99.207455454695406</v>
+      </c>
+      <c r="L47">
+        <v>0.62649556021687081</v>
+      </c>
+      <c r="M47">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N47">
+        <v>99.66498312203889</v>
+      </c>
+      <c r="O47">
+        <v>5292.2</v>
+      </c>
+      <c r="P47">
+        <v>4965.3290122609196</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>9816</v>
+      </c>
+      <c r="S47">
+        <v>0.52922000000000002</v>
+      </c>
+      <c r="T47">
+        <v>0.49653290122609189</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0.98160000000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="20"/>
+      <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C44">
-        <v>355.8</v>
-      </c>
-      <c r="D44">
-        <v>47.060599231204023</v>
-      </c>
-      <c r="E44">
-        <v>273</v>
-      </c>
-      <c r="F44">
-        <v>383</v>
-      </c>
-      <c r="H44" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="21"/>
-      <c r="B45" s="1" t="s">
+      <c r="C48">
+        <v>350</v>
+      </c>
+      <c r="D48">
+        <v>8.1853527718724521</v>
+      </c>
+      <c r="E48">
+        <v>341</v>
+      </c>
+      <c r="F48">
+        <v>363</v>
+      </c>
+      <c r="G48">
+        <v>0.44673838615417483</v>
+      </c>
+      <c r="H48">
+        <v>2.4257010688018471E-2</v>
+      </c>
+      <c r="I48">
+        <v>0.42199993133544922</v>
+      </c>
+      <c r="J48">
+        <v>0.48013997077941889</v>
+      </c>
+      <c r="K48">
+        <v>99.00644532791874</v>
+      </c>
+      <c r="L48">
+        <v>0.44299925901262233</v>
+      </c>
+      <c r="M48">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N48">
+        <v>99.329966244077795</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="20"/>
+      <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C45">
-        <v>303.60000000000002</v>
-      </c>
-      <c r="D45">
-        <v>33.738701812606827</v>
-      </c>
-      <c r="E45">
-        <v>272</v>
-      </c>
-      <c r="F45">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="21"/>
-      <c r="B46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="5">
-        <v>341.6</v>
-      </c>
-      <c r="D46">
-        <v>40.457384987168901</v>
-      </c>
-      <c r="E46">
-        <v>275</v>
-      </c>
-      <c r="F46">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="22"/>
-      <c r="B47" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="26">
-        <v>296.2</v>
-      </c>
-      <c r="D47">
-        <v>15.6588633048507</v>
-      </c>
-      <c r="E47">
-        <v>271</v>
-      </c>
-      <c r="F47">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="9">
-        <v>536</v>
-      </c>
-      <c r="E48">
-        <v>536</v>
-      </c>
-      <c r="F48">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="21"/>
-      <c r="B49" s="1"/>
+      <c r="C49">
+        <v>341.2</v>
+      </c>
+      <c r="D49">
+        <v>30.792856314411619</v>
+      </c>
+      <c r="E49">
+        <v>291</v>
+      </c>
+      <c r="F49">
+        <v>374</v>
+      </c>
+      <c r="G49">
+        <v>2.0920482158660891</v>
+      </c>
+      <c r="H49">
+        <v>4.9527176530464713E-2</v>
+      </c>
+      <c r="I49">
+        <v>2.0406944751739502</v>
+      </c>
+      <c r="J49">
+        <v>2.173589706420898</v>
+      </c>
+      <c r="K49">
+        <v>99.140452079103184</v>
+      </c>
+      <c r="L49">
+        <v>0.58163923812625273</v>
+      </c>
+      <c r="M49">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N49">
+        <v>99.66498312203889</v>
+      </c>
+      <c r="O49">
+        <v>6227.4</v>
+      </c>
+      <c r="P49">
+        <v>3541.936024266955</v>
+      </c>
+      <c r="Q49">
+        <v>24</v>
+      </c>
+      <c r="R49">
+        <v>8988</v>
+      </c>
+      <c r="S49">
+        <v>0.62274000000000007</v>
+      </c>
+      <c r="T49">
+        <v>0.35419360242669551</v>
+      </c>
+      <c r="U49">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="V49">
+        <v>0.89880000000000004</v>
+      </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="4">
+        <v>364</v>
+      </c>
+      <c r="D50">
+        <v>10.977249200050069</v>
+      </c>
+      <c r="E50">
+        <v>353</v>
+      </c>
+      <c r="F50">
+        <v>378</v>
+      </c>
+      <c r="G50">
+        <v>2.5422342777252198</v>
+      </c>
+      <c r="H50">
+        <v>0.13609258250657569</v>
+      </c>
+      <c r="I50">
+        <v>2.344831228256226</v>
+      </c>
+      <c r="J50">
+        <v>2.713082075119019</v>
+      </c>
+      <c r="K50">
+        <v>99.302212537182712</v>
+      </c>
+      <c r="L50">
+        <v>0.46764901923288787</v>
+      </c>
+      <c r="M50">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N50">
+        <v>99.66498312203889</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="5">
+        <v>348</v>
+      </c>
+      <c r="E51">
+        <v>348</v>
+      </c>
+      <c r="F51">
+        <v>348</v>
+      </c>
+      <c r="G51">
+        <v>2.0109350681304932</v>
+      </c>
+      <c r="I51">
+        <v>2.0109350681304932</v>
+      </c>
+      <c r="J51">
+        <v>2.0109350681304932</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
+      </c>
+      <c r="M51">
+        <v>100</v>
+      </c>
+      <c r="N51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="20"/>
+      <c r="B52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>440</v>
+      </c>
+      <c r="D52">
+        <v>13.56465996625054</v>
+      </c>
+      <c r="E52">
+        <v>427</v>
+      </c>
+      <c r="F52">
+        <v>462</v>
+      </c>
+      <c r="G52">
+        <v>1.569951629638672</v>
+      </c>
+      <c r="H52">
+        <v>0.17178170640153009</v>
+      </c>
+      <c r="I52">
+        <v>1.4821562767028811</v>
+      </c>
+      <c r="J52">
+        <v>1.876860618591309</v>
+      </c>
+      <c r="K52">
+        <v>99.376154339498683</v>
+      </c>
+      <c r="L52">
+        <v>0.27128053525298479</v>
+      </c>
+      <c r="M52">
+        <v>98.890872965260115</v>
+      </c>
+      <c r="N52">
+        <v>99.497474683058343</v>
+      </c>
+      <c r="O52">
+        <v>1770</v>
+      </c>
+      <c r="P52">
+        <v>3957.8403201746278</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>8850</v>
+      </c>
+      <c r="S52">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="T52">
+        <v>0.39578403201746282</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0.88500000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="20"/>
+      <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C50">
-        <v>453</v>
-      </c>
-      <c r="D50">
-        <v>43.550736694878843</v>
-      </c>
-      <c r="E50">
-        <v>396</v>
-      </c>
-      <c r="F50">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="21"/>
-      <c r="B51" s="1" t="s">
+      <c r="C53">
+        <v>428.6</v>
+      </c>
+      <c r="D53">
+        <v>10.8535708409721</v>
+      </c>
+      <c r="E53">
+        <v>414</v>
+      </c>
+      <c r="F53">
+        <v>442</v>
+      </c>
+      <c r="G53">
+        <v>0.6146029949188232</v>
+      </c>
+      <c r="H53">
+        <v>3.3875756563466468E-2</v>
+      </c>
+      <c r="I53">
+        <v>0.58013224601745605</v>
+      </c>
+      <c r="J53">
+        <v>0.65940022468566895</v>
+      </c>
+      <c r="K53">
+        <v>99.376154339498683</v>
+      </c>
+      <c r="L53">
+        <v>0.27128053525298951</v>
+      </c>
+      <c r="M53">
+        <v>98.890872965260115</v>
+      </c>
+      <c r="N53">
+        <v>99.497474683058343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="20"/>
+      <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C51">
-        <v>440.6</v>
-      </c>
-      <c r="D51">
-        <v>49.505555243830969</v>
-      </c>
-      <c r="E51">
-        <v>362</v>
-      </c>
-      <c r="F51">
-        <v>484</v>
-      </c>
-      <c r="H51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="21"/>
-      <c r="B52" s="1" t="s">
+      <c r="C54">
+        <v>435.8</v>
+      </c>
+      <c r="D54">
+        <v>16.574076143182161</v>
+      </c>
+      <c r="E54">
+        <v>412</v>
+      </c>
+      <c r="F54">
+        <v>457</v>
+      </c>
+      <c r="G54">
+        <v>2.462710666656494</v>
+      </c>
+      <c r="H54">
+        <v>0.17382025759038841</v>
+      </c>
+      <c r="I54">
+        <v>2.1660397052764888</v>
+      </c>
+      <c r="J54">
+        <v>2.6223850250244141</v>
+      </c>
+      <c r="K54">
+        <v>99.254833995939038</v>
+      </c>
+      <c r="L54">
+        <v>0.33224944425945901</v>
+      </c>
+      <c r="M54">
+        <v>98.890872965260115</v>
+      </c>
+      <c r="N54">
+        <v>99.497474683058343</v>
+      </c>
+      <c r="O54">
+        <v>6910.6</v>
+      </c>
+      <c r="P54">
+        <v>1412.2348600710859</v>
+      </c>
+      <c r="Q54">
+        <v>5421</v>
+      </c>
+      <c r="R54">
+        <v>8995</v>
+      </c>
+      <c r="S54">
+        <v>0.69106000000000001</v>
+      </c>
+      <c r="T54">
+        <v>0.1412234860071086</v>
+      </c>
+      <c r="U54">
+        <v>0.54210000000000003</v>
+      </c>
+      <c r="V54">
+        <v>0.89949999999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="21"/>
+      <c r="B55" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C52">
-        <v>374.2</v>
-      </c>
-      <c r="D52">
-        <v>39.079406341447921</v>
-      </c>
-      <c r="E52">
-        <v>338</v>
-      </c>
-      <c r="F52">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="22"/>
-      <c r="B53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="26">
-        <v>396.75</v>
-      </c>
-      <c r="D53">
-        <v>41.772199686713492</v>
-      </c>
-      <c r="E53">
-        <v>354</v>
-      </c>
-      <c r="F53">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="7">
-        <v>303</v>
-      </c>
-      <c r="E54">
-        <v>303</v>
-      </c>
-      <c r="F54">
-        <v>303</v>
-      </c>
-      <c r="G54">
-        <v>2.050655841827393</v>
-      </c>
-      <c r="I54">
-        <v>2.050655841827393</v>
-      </c>
-      <c r="J54">
-        <v>2.050655841827393</v>
-      </c>
-      <c r="K54">
-        <v>99.621165057908925</v>
-      </c>
-      <c r="M54">
-        <v>99.621165057908925</v>
-      </c>
-      <c r="N54">
-        <v>99.621165057908925</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
-      <c r="B55" s="1"/>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56">
-        <v>352.2</v>
-      </c>
-      <c r="D56">
-        <v>13.367871932360821</v>
-      </c>
-      <c r="E56">
-        <v>339</v>
-      </c>
-      <c r="F56">
-        <v>372</v>
-      </c>
-      <c r="G56">
-        <v>1.299343872070313</v>
-      </c>
-      <c r="H56">
-        <v>0.23668983572394969</v>
-      </c>
-      <c r="I56">
-        <v>1.0473401546478269</v>
-      </c>
-      <c r="J56">
-        <v>1.566922664642334</v>
-      </c>
-      <c r="K56">
-        <v>99.207455454695406</v>
-      </c>
-      <c r="L56">
-        <v>0.62649556021687081</v>
-      </c>
-      <c r="M56">
-        <v>98.521163953680173</v>
-      </c>
-      <c r="N56">
-        <v>99.66498312203889</v>
-      </c>
-      <c r="O56">
-        <v>5292.2</v>
-      </c>
-      <c r="P56">
-        <v>4965.3290122609196</v>
-      </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-      <c r="R56">
-        <v>9816</v>
-      </c>
-      <c r="S56">
-        <v>0.52922000000000002</v>
-      </c>
-      <c r="T56">
-        <v>0.49653290122609189</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>0.98160000000000003</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
-      <c r="B57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57">
-        <v>350</v>
-      </c>
-      <c r="D57">
-        <v>8.1853527718724521</v>
-      </c>
-      <c r="E57">
-        <v>341</v>
-      </c>
-      <c r="F57">
-        <v>363</v>
-      </c>
-      <c r="G57">
-        <v>0.44673838615417483</v>
-      </c>
-      <c r="H57">
-        <v>2.4257010688018471E-2</v>
-      </c>
-      <c r="I57">
-        <v>0.42199993133544922</v>
-      </c>
-      <c r="J57">
-        <v>0.48013997077941889</v>
-      </c>
-      <c r="K57">
-        <v>99.00644532791874</v>
-      </c>
-      <c r="L57">
-        <v>0.44299925901262233</v>
-      </c>
-      <c r="M57">
-        <v>98.521163953680173</v>
-      </c>
-      <c r="N57">
-        <v>99.329966244077795</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A58" s="13"/>
-      <c r="B58" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58">
-        <v>341.2</v>
-      </c>
-      <c r="D58">
-        <v>30.792856314411619</v>
-      </c>
-      <c r="E58">
-        <v>291</v>
-      </c>
-      <c r="F58">
-        <v>374</v>
-      </c>
-      <c r="G58">
-        <v>2.0920482158660891</v>
-      </c>
-      <c r="H58">
-        <v>4.9527176530464713E-2</v>
-      </c>
-      <c r="I58">
-        <v>2.0406944751739502</v>
-      </c>
-      <c r="J58">
-        <v>2.173589706420898</v>
-      </c>
-      <c r="K58">
-        <v>99.140452079103184</v>
-      </c>
-      <c r="L58">
-        <v>0.58163923812625273</v>
-      </c>
-      <c r="M58">
-        <v>98.521163953680173</v>
-      </c>
-      <c r="N58">
-        <v>99.66498312203889</v>
-      </c>
-      <c r="O58">
-        <v>6227.4</v>
-      </c>
-      <c r="P58">
-        <v>3541.936024266955</v>
-      </c>
-      <c r="Q58">
-        <v>24</v>
-      </c>
-      <c r="R58">
-        <v>8988</v>
-      </c>
-      <c r="S58">
-        <v>0.62274000000000007</v>
-      </c>
-      <c r="T58">
-        <v>0.35419360242669551</v>
-      </c>
-      <c r="U58">
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="V58">
-        <v>0.89880000000000004</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="6">
-        <v>364</v>
-      </c>
-      <c r="D59">
-        <v>10.977249200050069</v>
-      </c>
-      <c r="E59">
-        <v>353</v>
-      </c>
-      <c r="F59">
-        <v>378</v>
-      </c>
-      <c r="G59">
-        <v>2.5422342777252198</v>
-      </c>
-      <c r="H59">
-        <v>0.13609258250657569</v>
-      </c>
-      <c r="I59">
-        <v>2.344831228256226</v>
-      </c>
-      <c r="J59">
-        <v>2.713082075119019</v>
-      </c>
-      <c r="K59">
-        <v>99.302212537182712</v>
-      </c>
-      <c r="L59">
-        <v>0.46764901923288787</v>
-      </c>
-      <c r="M59">
-        <v>98.521163953680173</v>
-      </c>
-      <c r="N59">
-        <v>99.66498312203889</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="7">
-        <v>348</v>
-      </c>
-      <c r="E60">
-        <v>348</v>
-      </c>
-      <c r="F60">
-        <v>348</v>
-      </c>
-      <c r="G60">
-        <v>2.0109350681304932</v>
-      </c>
-      <c r="I60">
-        <v>2.0109350681304932</v>
-      </c>
-      <c r="J60">
-        <v>2.0109350681304932</v>
-      </c>
-      <c r="K60">
-        <v>100</v>
-      </c>
-      <c r="M60">
-        <v>100</v>
-      </c>
-      <c r="N60">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="1"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
-      <c r="B62" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62">
-        <v>440</v>
-      </c>
-      <c r="D62">
-        <v>13.56465996625054</v>
-      </c>
-      <c r="E62">
-        <v>427</v>
-      </c>
-      <c r="F62">
-        <v>462</v>
-      </c>
-      <c r="G62">
-        <v>1.569951629638672</v>
-      </c>
-      <c r="H62">
-        <v>0.17178170640153009</v>
-      </c>
-      <c r="I62">
-        <v>1.4821562767028811</v>
-      </c>
-      <c r="J62">
-        <v>1.876860618591309</v>
-      </c>
-      <c r="K62">
+      <c r="C55" s="4">
+        <v>448.8</v>
+      </c>
+      <c r="D55">
+        <v>19.81665965797464</v>
+      </c>
+      <c r="E55">
+        <v>420</v>
+      </c>
+      <c r="F55">
+        <v>468</v>
+      </c>
+      <c r="G55">
+        <v>2.841660356521607</v>
+      </c>
+      <c r="H55">
+        <v>0.29428370567911449</v>
+      </c>
+      <c r="I55">
+        <v>2.5950603485107422</v>
+      </c>
+      <c r="J55">
+        <v>3.3389179706573491</v>
+      </c>
+      <c r="K55">
         <v>99.376154339498683</v>
       </c>
-      <c r="L62">
-        <v>0.27128053525298479</v>
-      </c>
-      <c r="M62">
+      <c r="L55">
+        <v>0.27128053525298951</v>
+      </c>
+      <c r="M55">
         <v>98.890872965260115</v>
       </c>
-      <c r="N62">
-        <v>99.497474683058343</v>
-      </c>
-      <c r="O62">
-        <v>1770</v>
-      </c>
-      <c r="P62">
-        <v>3957.8403201746278</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>8850</v>
-      </c>
-      <c r="S62">
-        <v>0.17699999999999999</v>
-      </c>
-      <c r="T62">
-        <v>0.39578403201746282</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0.88500000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63">
-        <v>428.6</v>
-      </c>
-      <c r="D63">
-        <v>10.8535708409721</v>
-      </c>
-      <c r="E63">
-        <v>414</v>
-      </c>
-      <c r="F63">
-        <v>442</v>
-      </c>
-      <c r="G63">
-        <v>0.6146029949188232</v>
-      </c>
-      <c r="H63">
-        <v>3.3875756563466468E-2</v>
-      </c>
-      <c r="I63">
-        <v>0.58013224601745605</v>
-      </c>
-      <c r="J63">
-        <v>0.65940022468566895</v>
-      </c>
-      <c r="K63">
-        <v>99.376154339498683</v>
-      </c>
-      <c r="L63">
-        <v>0.27128053525298951</v>
-      </c>
-      <c r="M63">
-        <v>98.890872965260115</v>
-      </c>
-      <c r="N63">
-        <v>99.497474683058343</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A64" s="13"/>
-      <c r="B64" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64">
-        <v>435.8</v>
-      </c>
-      <c r="D64">
-        <v>16.574076143182161</v>
-      </c>
-      <c r="E64">
-        <v>412</v>
-      </c>
-      <c r="F64">
-        <v>457</v>
-      </c>
-      <c r="G64">
-        <v>2.462710666656494</v>
-      </c>
-      <c r="H64">
-        <v>0.17382025759038841</v>
-      </c>
-      <c r="I64">
-        <v>2.1660397052764888</v>
-      </c>
-      <c r="J64">
-        <v>2.6223850250244141</v>
-      </c>
-      <c r="K64">
-        <v>99.254833995939038</v>
-      </c>
-      <c r="L64">
-        <v>0.33224944425945901</v>
-      </c>
-      <c r="M64">
-        <v>98.890872965260115</v>
-      </c>
-      <c r="N64">
-        <v>99.497474683058343</v>
-      </c>
-      <c r="O64">
-        <v>6910.6</v>
-      </c>
-      <c r="P64">
-        <v>1412.2348600710859</v>
-      </c>
-      <c r="Q64">
-        <v>5421</v>
-      </c>
-      <c r="R64">
-        <v>8995</v>
-      </c>
-      <c r="S64">
-        <v>0.69106000000000001</v>
-      </c>
-      <c r="T64">
-        <v>0.1412234860071086</v>
-      </c>
-      <c r="U64">
-        <v>0.54210000000000003</v>
-      </c>
-      <c r="V64">
-        <v>0.89949999999999997</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="6">
-        <v>448.8</v>
-      </c>
-      <c r="D65">
-        <v>19.81665965797464</v>
-      </c>
-      <c r="E65">
-        <v>420</v>
-      </c>
-      <c r="F65">
-        <v>468</v>
-      </c>
-      <c r="G65">
-        <v>2.841660356521607</v>
-      </c>
-      <c r="H65">
-        <v>0.29428370567911449</v>
-      </c>
-      <c r="I65">
-        <v>2.5950603485107422</v>
-      </c>
-      <c r="J65">
-        <v>3.3389179706573491</v>
-      </c>
-      <c r="K65">
-        <v>99.376154339498683</v>
-      </c>
-      <c r="L65">
-        <v>0.27128053525298951</v>
-      </c>
-      <c r="M65">
-        <v>98.890872965260115</v>
-      </c>
-      <c r="N65">
+      <c r="N55">
         <v>99.497474683058343</v>
       </c>
     </row>
@@ -3363,19 +3438,19 @@
   <mergeCells count="15">
     <mergeCell ref="O3:R3"/>
     <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A54:A59"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A60:A65"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A51:A55"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:N3"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="A42:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A21:A25"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A16:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3383,7 +3458,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58126609-257A-4A45-B385-DFB3BFE448A7}">
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
@@ -3392,41 +3467,41 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
@@ -3500,13 +3575,13 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>14</v>
+      <c r="A6" s="22" t="s">
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>376</v>
       </c>
       <c r="E6">
@@ -3517,11 +3592,11 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="6">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4">
         <v>390.2</v>
       </c>
       <c r="D7">
@@ -3535,9 +3610,9 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>361.6</v>
@@ -3553,9 +3628,9 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>360.8</v>
@@ -3571,9 +3646,9 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10">
         <v>377.8</v>
@@ -3590,12 +3665,12 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>558</v>
       </c>
       <c r="E11">
@@ -3608,7 +3683,7 @@
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>500.6</v>
@@ -3626,7 +3701,7 @@
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>489.6</v>
@@ -3644,7 +3719,7 @@
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>482.2</v>
@@ -3662,7 +3737,7 @@
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>509</v>
@@ -3678,13 +3753,13 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>16</v>
+      <c r="A16" s="22" t="s">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>315</v>
       </c>
       <c r="E16">
@@ -3695,11 +3770,11 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3">
         <v>343.2</v>
       </c>
       <c r="D17">
@@ -3713,9 +3788,9 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
+      <c r="A18" s="22"/>
       <c r="B18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <v>325.60000000000002</v>
@@ -3726,17 +3801,17 @@
       <c r="E18">
         <v>309</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="6">
         <v>361</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>326.39999999999998</v>
@@ -3747,16 +3822,16 @@
       <c r="E19">
         <v>302</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="6">
         <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="6">
+        <v>12</v>
+      </c>
+      <c r="C20" s="4">
         <v>341.8</v>
       </c>
       <c r="D20">
@@ -3770,13 +3845,13 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>15</v>
+      <c r="A21" s="22" t="s">
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>444</v>
       </c>
       <c r="E21">
@@ -3787,11 +3862,11 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
+        <v>9</v>
+      </c>
+      <c r="C22" s="4">
         <v>454</v>
       </c>
       <c r="D22">
@@ -3805,9 +3880,9 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>422.2</v>
@@ -3823,9 +3898,9 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
+      <c r="A24" s="22"/>
       <c r="B24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
         <v>389.6</v>
@@ -3841,9 +3916,9 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>417.4</v>
@@ -3859,13 +3934,13 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>18</v>
+      <c r="A26" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>453</v>
       </c>
       <c r="E26">
@@ -3876,9 +3951,9 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27">
         <v>474</v>
@@ -3894,9 +3969,9 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>445.6</v>
@@ -3912,49 +3987,49 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="3">
+        <v>451.6</v>
+      </c>
+      <c r="D29" s="10">
+        <v>23.807561823924772</v>
+      </c>
+      <c r="E29" s="6">
+        <v>417</v>
+      </c>
+      <c r="F29" s="6">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
+      <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="5">
-        <v>451.6</v>
-      </c>
-      <c r="D29" s="15">
-        <v>23.807561823924772</v>
-      </c>
-      <c r="E29" s="8">
-        <v>417</v>
-      </c>
-      <c r="F29" s="8">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="C30" s="4">
         <v>493</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="10">
         <v>28.416544476765651</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="6">
         <v>460</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <v>535</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="7">
         <v>622</v>
       </c>
       <c r="E31">
@@ -3967,7 +4042,7 @@
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
       <c r="B32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32">
         <v>576</v>
@@ -3985,7 +4060,7 @@
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>557.79999999999995</v>
@@ -4003,7 +4078,7 @@
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34">
         <v>550.4</v>
@@ -4021,9 +4096,9 @@
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="6">
+        <v>12</v>
+      </c>
+      <c r="C35" s="4">
         <v>592.20000000000005</v>
       </c>
       <c r="D35">
@@ -4038,12 +4113,12 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="7">
         <v>414</v>
       </c>
       <c r="E36">
@@ -4056,7 +4131,7 @@
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37">
         <v>330.6</v>
@@ -4074,7 +4149,7 @@
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38">
         <v>322.2</v>
@@ -4092,7 +4167,7 @@
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39">
         <v>289.2</v>
@@ -4110,7 +4185,7 @@
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40">
         <v>306.2</v>
@@ -4127,12 +4202,12 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="7">
         <v>536</v>
       </c>
       <c r="E41">
@@ -4145,7 +4220,7 @@
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>442.4</v>
@@ -4163,7 +4238,7 @@
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43">
         <v>434.8</v>
@@ -4181,7 +4256,7 @@
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44">
         <v>401.4</v>
@@ -4199,7 +4274,7 @@
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45">
         <v>405.4</v>
@@ -4215,8 +4290,8 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>24</v>
+      <c r="A46" s="15" t="s">
+        <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>8</v>
@@ -4250,347 +4325,472 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="1" t="s">
-        <v>11</v>
+      <c r="A47" s="15"/>
+      <c r="B47" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="C47">
+        <v>433.4</v>
+      </c>
+      <c r="D47">
+        <v>32.315630892804812</v>
+      </c>
+      <c r="E47">
+        <v>395</v>
+      </c>
+      <c r="F47">
+        <v>473</v>
+      </c>
+      <c r="G47">
+        <v>8.4886989116668694</v>
+      </c>
+      <c r="H47">
+        <v>0.29076145233050299</v>
+      </c>
+      <c r="I47">
+        <v>7.9804027080535889</v>
+      </c>
+      <c r="J47">
+        <v>8.7150270938873291</v>
+      </c>
+      <c r="K47">
+        <v>99.083261120685236</v>
+      </c>
+      <c r="L47">
+        <v>0.39179018615642902</v>
+      </c>
+      <c r="M47">
+        <v>98.639610306789265</v>
+      </c>
+      <c r="N47">
+        <v>99.497474683058343</v>
+      </c>
+      <c r="O47">
+        <v>45211.8</v>
+      </c>
+      <c r="P47">
+        <v>7956.7748302939935</v>
+      </c>
+      <c r="Q47">
+        <v>31203</v>
+      </c>
+      <c r="R47">
+        <v>49848</v>
+      </c>
+      <c r="S47">
+        <v>0.90423600000000004</v>
+      </c>
+      <c r="T47">
+        <v>0.15913549660587981</v>
+      </c>
+      <c r="U47">
+        <v>0.62406000000000006</v>
+      </c>
+      <c r="V47">
+        <v>0.99695999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="15"/>
+      <c r="B48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48">
         <v>349.2</v>
       </c>
-      <c r="D47">
+      <c r="D48">
         <v>11.344602240713421</v>
       </c>
-      <c r="E47">
+      <c r="E48">
         <v>338</v>
       </c>
-      <c r="F47">
+      <c r="F48">
         <v>365</v>
       </c>
-      <c r="G47">
+      <c r="G48">
         <v>2.042593812942505</v>
       </c>
-      <c r="H47">
+      <c r="H48">
         <v>8.1485932462665292E-2</v>
       </c>
-      <c r="I47">
+      <c r="I48">
         <v>1.937538623809814</v>
       </c>
-      <c r="J47">
+      <c r="J48">
         <v>2.1535623073577881</v>
       </c>
-      <c r="K47">
+      <c r="K48">
         <v>99.23520916159049</v>
       </c>
-      <c r="L47">
+      <c r="L48">
         <v>0.42470664289121618</v>
       </c>
-      <c r="M47">
+      <c r="M48">
         <v>98.521163953680173</v>
-      </c>
-      <c r="N47">
-        <v>99.66498312203889</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48">
-        <v>328.2</v>
-      </c>
-      <c r="D48">
-        <v>14.30734077318354</v>
-      </c>
-      <c r="E48">
-        <v>304</v>
-      </c>
-      <c r="F48">
-        <v>341</v>
-      </c>
-      <c r="G48">
-        <v>10.9322142124176</v>
-      </c>
-      <c r="H48">
-        <v>0.41985823894124658</v>
-      </c>
-      <c r="I48">
-        <v>10.38349318504333</v>
-      </c>
-      <c r="J48">
-        <v>11.51608777046204</v>
-      </c>
-      <c r="K48">
-        <v>99.396969619670017</v>
-      </c>
-      <c r="L48">
-        <v>0.14982410254615131</v>
-      </c>
-      <c r="M48">
-        <v>99.329966244077795</v>
       </c>
       <c r="N48">
         <v>99.66498312203889</v>
       </c>
-      <c r="O48">
-        <v>43068.4</v>
-      </c>
-      <c r="P48">
-        <v>2427.3581935923671</v>
-      </c>
-      <c r="Q48">
-        <v>38914</v>
-      </c>
-      <c r="R48">
-        <v>44987</v>
-      </c>
-      <c r="S48">
-        <v>0.86136800000000002</v>
-      </c>
-      <c r="T48">
-        <v>4.8547163871847349E-2</v>
-      </c>
-      <c r="U48">
-        <v>0.77827999999999997</v>
-      </c>
-      <c r="V48">
-        <v>0.89973999999999998</v>
-      </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
+      <c r="A49" s="15"/>
       <c r="B49" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C49">
-        <v>372.2</v>
+        <v>328.2</v>
       </c>
       <c r="D49">
-        <v>17.108477430794359</v>
+        <v>14.30734077318354</v>
       </c>
       <c r="E49">
-        <v>358</v>
+        <v>304</v>
       </c>
       <c r="F49">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="G49">
-        <v>13.292735004425049</v>
+        <v>10.9322142124176</v>
       </c>
       <c r="H49">
-        <v>0.49452774098687058</v>
+        <v>0.41985823894124658</v>
       </c>
       <c r="I49">
-        <v>12.802443981170651</v>
+        <v>10.38349318504333</v>
       </c>
       <c r="J49">
-        <v>13.975799322128299</v>
+        <v>11.51608777046204</v>
       </c>
       <c r="K49">
-        <v>99.045694996615879</v>
+        <v>99.396969619670017</v>
       </c>
       <c r="L49">
-        <v>0.5816392381262494</v>
+        <v>0.14982410254615131</v>
       </c>
       <c r="M49">
-        <v>98.521163953680173</v>
+        <v>99.329966244077795</v>
       </c>
       <c r="N49">
         <v>99.66498312203889</v>
       </c>
+      <c r="O49">
+        <v>43068.4</v>
+      </c>
+      <c r="P49">
+        <v>2427.3581935923671</v>
+      </c>
+      <c r="Q49">
+        <v>38914</v>
+      </c>
+      <c r="R49">
+        <v>44987</v>
+      </c>
+      <c r="S49">
+        <v>0.86136800000000002</v>
+      </c>
+      <c r="T49">
+        <v>4.8547163871847349E-2</v>
+      </c>
+      <c r="U49">
+        <v>0.77827999999999997</v>
+      </c>
+      <c r="V49">
+        <v>0.89973999999999998</v>
+      </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>30</v>
+      <c r="A50" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50">
+        <v>372.2</v>
+      </c>
+      <c r="D50">
+        <v>17.108477430794359</v>
+      </c>
+      <c r="E50">
+        <v>358</v>
+      </c>
+      <c r="F50">
+        <v>395</v>
+      </c>
+      <c r="G50">
+        <v>13.292735004425049</v>
+      </c>
+      <c r="H50">
+        <v>0.49452774098687058</v>
+      </c>
+      <c r="I50">
+        <v>12.802443981170651</v>
+      </c>
+      <c r="J50">
+        <v>13.975799322128299</v>
+      </c>
+      <c r="K50">
+        <v>99.045694996615879</v>
+      </c>
+      <c r="L50">
+        <v>0.5816392381262494</v>
+      </c>
+      <c r="M50">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N50">
+        <v>99.66498312203889</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="15"/>
+      <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C50">
+      <c r="C51">
         <v>348</v>
       </c>
-      <c r="E50">
+      <c r="E51">
         <v>348</v>
       </c>
-      <c r="F50">
+      <c r="F51">
         <v>348</v>
       </c>
-      <c r="G50">
+      <c r="G51">
         <v>2.010546207427979</v>
       </c>
-      <c r="I50">
+      <c r="I51">
         <v>2.010546207427979</v>
       </c>
-      <c r="J50">
+      <c r="J51">
         <v>2.010546207427979</v>
       </c>
-      <c r="K50">
+      <c r="K51">
         <v>100</v>
       </c>
-      <c r="M50">
+      <c r="M51">
         <v>100</v>
       </c>
-      <c r="N50">
+      <c r="N51">
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="15"/>
+      <c r="B52" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52">
+        <v>337.2</v>
+      </c>
+      <c r="D52">
+        <v>20.425474290698851</v>
+      </c>
+      <c r="E52">
+        <v>315</v>
+      </c>
+      <c r="F52">
+        <v>364</v>
+      </c>
+      <c r="G52">
+        <v>5.968729782104492</v>
+      </c>
+      <c r="H52">
+        <v>0.81142093741931975</v>
+      </c>
+      <c r="I52">
+        <v>4.8741962909698486</v>
+      </c>
+      <c r="J52">
+        <v>6.7957751750946036</v>
+      </c>
+      <c r="K52">
+        <v>98.911688245431449</v>
+      </c>
+      <c r="L52">
+        <v>0.54770825322842309</v>
+      </c>
+      <c r="M52">
+        <v>98.521163953680173</v>
+      </c>
+      <c r="N52">
+        <v>99.66498312203889</v>
+      </c>
+      <c r="O52">
+        <v>28289.8</v>
+      </c>
+      <c r="P52">
+        <v>18819.37859494835</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>49489</v>
+      </c>
+      <c r="S52">
+        <v>0.56579599999999997</v>
+      </c>
+      <c r="T52">
+        <v>0.37638757189896688</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0.98977999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="15"/>
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53">
         <v>421.8</v>
       </c>
-      <c r="D51">
+      <c r="D53">
         <v>14.37706506906051</v>
       </c>
-      <c r="E51">
+      <c r="E53">
         <v>409</v>
       </c>
-      <c r="F51">
+      <c r="F53">
         <v>445</v>
       </c>
-      <c r="G51">
+      <c r="G53">
         <v>2.4749284744262701</v>
       </c>
-      <c r="H51">
+      <c r="H53">
         <v>0.1293654713889798</v>
       </c>
-      <c r="I51">
+      <c r="I53">
         <v>2.3787322044372559</v>
       </c>
-      <c r="J51">
+      <c r="J53">
         <v>2.6946332454681401</v>
       </c>
-      <c r="K51">
+      <c r="K53">
         <v>99.254833995939052</v>
       </c>
-      <c r="L51">
+      <c r="L53">
         <v>0.33224944425946762</v>
-      </c>
-      <c r="M51">
-        <v>98.890872965260115</v>
-      </c>
-      <c r="N51">
-        <v>99.497474683058343</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52">
-        <v>437.2</v>
-      </c>
-      <c r="D52">
-        <v>19.395875850293539</v>
-      </c>
-      <c r="E52">
-        <v>423</v>
-      </c>
-      <c r="F52">
-        <v>471</v>
-      </c>
-      <c r="G52">
-        <v>14.2135486125946</v>
-      </c>
-      <c r="H52">
-        <v>0.82753743350749931</v>
-      </c>
-      <c r="I52">
-        <v>13.5012800693512</v>
-      </c>
-      <c r="J52">
-        <v>15.490762710571291</v>
-      </c>
-      <c r="K52">
-        <v>99.376154339498683</v>
-      </c>
-      <c r="L52">
-        <v>0.27128053525298362</v>
-      </c>
-      <c r="M52">
-        <v>98.890872965260115</v>
-      </c>
-      <c r="N52">
-        <v>99.497474683058314</v>
-      </c>
-      <c r="O52">
-        <v>41744.800000000003</v>
-      </c>
-      <c r="P52">
-        <v>1705.4866460925459</v>
-      </c>
-      <c r="Q52">
-        <v>38982</v>
-      </c>
-      <c r="R52">
-        <v>43571</v>
-      </c>
-      <c r="S52">
-        <v>0.83489599999999997</v>
-      </c>
-      <c r="T52">
-        <v>3.4109732921850877E-2</v>
-      </c>
-      <c r="U52">
-        <v>0.77964</v>
-      </c>
-      <c r="V52">
-        <v>0.87141999999999997</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-      <c r="B53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53">
-        <v>441.6</v>
-      </c>
-      <c r="D53">
-        <v>7.7006493232713753</v>
-      </c>
-      <c r="E53">
-        <v>430</v>
-      </c>
-      <c r="F53">
-        <v>450</v>
-      </c>
-      <c r="G53">
-        <v>15.86496777534485</v>
-      </c>
-      <c r="H53">
-        <v>0.27356244209735892</v>
-      </c>
-      <c r="I53">
-        <v>15.63900184631348</v>
-      </c>
-      <c r="J53">
-        <v>16.302419662475589</v>
-      </c>
-      <c r="K53">
-        <v>99.376154339498683</v>
-      </c>
-      <c r="L53">
-        <v>0.27128053525298612</v>
       </c>
       <c r="M53">
         <v>98.890872965260115</v>
       </c>
       <c r="N53">
+        <v>99.497474683058343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54">
+        <v>437.2</v>
+      </c>
+      <c r="D54">
+        <v>19.395875850293539</v>
+      </c>
+      <c r="E54">
+        <v>423</v>
+      </c>
+      <c r="F54">
+        <v>471</v>
+      </c>
+      <c r="G54">
+        <v>14.2135486125946</v>
+      </c>
+      <c r="H54">
+        <v>0.82753743350749931</v>
+      </c>
+      <c r="I54">
+        <v>13.5012800693512</v>
+      </c>
+      <c r="J54">
+        <v>15.490762710571291</v>
+      </c>
+      <c r="K54">
+        <v>99.376154339498683</v>
+      </c>
+      <c r="L54">
+        <v>0.27128053525298362</v>
+      </c>
+      <c r="M54">
+        <v>98.890872965260115</v>
+      </c>
+      <c r="N54">
+        <v>99.497474683058314</v>
+      </c>
+      <c r="O54">
+        <v>41744.800000000003</v>
+      </c>
+      <c r="P54">
+        <v>1705.4866460925459</v>
+      </c>
+      <c r="Q54">
+        <v>38982</v>
+      </c>
+      <c r="R54">
+        <v>43571</v>
+      </c>
+      <c r="S54">
+        <v>0.83489599999999997</v>
+      </c>
+      <c r="T54">
+        <v>3.4109732921850877E-2</v>
+      </c>
+      <c r="U54">
+        <v>0.77964</v>
+      </c>
+      <c r="V54">
+        <v>0.87141999999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>441.6</v>
+      </c>
+      <c r="D55">
+        <v>7.7006493232713753</v>
+      </c>
+      <c r="E55">
+        <v>430</v>
+      </c>
+      <c r="F55">
+        <v>450</v>
+      </c>
+      <c r="G55">
+        <v>15.86496777534485</v>
+      </c>
+      <c r="H55">
+        <v>0.27356244209735892</v>
+      </c>
+      <c r="I55">
+        <v>15.63900184631348</v>
+      </c>
+      <c r="J55">
+        <v>16.302419662475589</v>
+      </c>
+      <c r="K55">
+        <v>99.376154339498683</v>
+      </c>
+      <c r="L55">
+        <v>0.27128053525298612</v>
+      </c>
+      <c r="M55">
+        <v>98.890872965260115</v>
+      </c>
+      <c r="N55">
         <v>99.497474683058314</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A36:A40"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A53"/>
@@ -4601,6 +4801,11 @@
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="A26:A30"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A36:A40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4608,7 +4813,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986CE34A-0472-4CC3-8683-488EBE5AEA7F}">
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -4617,41 +4822,41 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
@@ -4726,12 +4931,12 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>1220</v>
       </c>
       <c r="E6">
@@ -4765,64 +4970,64 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>998.4</v>
+        <v>1107.5999999999999</v>
       </c>
       <c r="D7">
-        <v>11.717508267545631</v>
+        <v>23.543576618687329</v>
       </c>
       <c r="E7">
-        <v>987</v>
+        <v>1079</v>
       </c>
       <c r="F7">
-        <v>1012</v>
+        <v>1132</v>
       </c>
       <c r="G7">
-        <v>28.72368664741516</v>
+        <v>34.728247737884523</v>
       </c>
       <c r="H7">
-        <v>0.48165842703336981</v>
+        <v>0.94078282635865174</v>
       </c>
       <c r="I7">
-        <v>28.221770286560059</v>
+        <v>33.39442253112793</v>
       </c>
       <c r="J7">
-        <v>29.460582256317139</v>
+        <v>35.671040534973137</v>
       </c>
       <c r="K7">
-        <v>99.859822611795806</v>
+        <v>99.666683758928428</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>0.21114599667222761</v>
       </c>
       <c r="M7">
-        <v>99.859822611795806</v>
+        <v>99.401755575069373</v>
       </c>
       <c r="N7">
-        <v>99.859822611795806</v>
+        <v>99.97947149678194</v>
       </c>
       <c r="O7">
-        <v>99340</v>
+        <v>99289.2</v>
       </c>
       <c r="P7">
-        <v>1113.173167121811</v>
+        <v>573.91262401170616</v>
       </c>
       <c r="Q7">
-        <v>97351</v>
+        <v>98451</v>
       </c>
       <c r="R7">
-        <v>99901</v>
+        <v>99913</v>
       </c>
       <c r="S7">
-        <v>0.99340032660581679</v>
+        <v>0.99289249563743043</v>
       </c>
       <c r="T7">
-        <v>1.1131279639208871E-2</v>
+        <v>5.7387786017441536E-3</v>
       </c>
       <c r="U7">
-        <v>0.97351113266992895</v>
+        <v>0.98451093311311044</v>
       </c>
       <c r="V7">
-        <v>0.99901007799371255</v>
+        <v>0.99913006959443251</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -4831,64 +5036,40 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>1107.5999999999999</v>
+        <v>1003.5</v>
       </c>
       <c r="D8">
-        <v>23.543576618687329</v>
+        <v>7.9372539331937739</v>
       </c>
       <c r="E8">
-        <v>1079</v>
+        <v>996</v>
       </c>
       <c r="F8">
-        <v>1132</v>
+        <v>1013</v>
       </c>
       <c r="G8">
-        <v>34.728247737884523</v>
+        <v>7.3043125867843628</v>
       </c>
       <c r="H8">
-        <v>0.94078282635865174</v>
+        <v>0.27078587796176662</v>
       </c>
       <c r="I8">
-        <v>33.39442253112793</v>
+        <v>7.0690782070159912</v>
       </c>
       <c r="J8">
-        <v>35.671040534973137</v>
+        <v>7.659520149230957</v>
       </c>
       <c r="K8">
-        <v>99.666683758928428</v>
+        <v>99.859822611795806</v>
       </c>
       <c r="L8">
-        <v>0.21114599667222761</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>99.401755575069373</v>
+        <v>99.859822611795806</v>
       </c>
       <c r="N8">
-        <v>99.97947149678194</v>
-      </c>
-      <c r="O8">
-        <v>99289.2</v>
-      </c>
-      <c r="P8">
-        <v>573.91262401170616</v>
-      </c>
-      <c r="Q8">
-        <v>98451</v>
-      </c>
-      <c r="R8">
-        <v>99913</v>
-      </c>
-      <c r="S8">
-        <v>0.99289249563743043</v>
-      </c>
-      <c r="T8">
-        <v>5.7387786017441536E-3</v>
-      </c>
-      <c r="U8">
-        <v>0.98451093311311044</v>
-      </c>
-      <c r="V8">
-        <v>0.99913006959443251</v>
+        <v>99.859822611795806</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -4897,40 +5078,64 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>1003.5</v>
-      </c>
-      <c r="D9">
-        <v>7.9372539331937739</v>
+        <v>1020.2</v>
+      </c>
+      <c r="D9" s="10">
+        <v>23.70021096952517</v>
       </c>
       <c r="E9">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="F9">
-        <v>1013</v>
+        <v>1062</v>
       </c>
       <c r="G9">
-        <v>7.3043125867843628</v>
+        <v>43.197508430480958</v>
       </c>
       <c r="H9">
-        <v>0.27078587796176662</v>
+        <v>3.7255837028210061</v>
       </c>
       <c r="I9">
-        <v>7.0690782070159912</v>
+        <v>38.572652578353882</v>
       </c>
       <c r="J9">
-        <v>7.659520149230957</v>
+        <v>48.984535217285163</v>
       </c>
       <c r="K9">
-        <v>99.859822611795806</v>
+        <v>99.883752388793027</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>5.35086080521971E-2</v>
       </c>
       <c r="M9">
         <v>99.859822611795806</v>
       </c>
       <c r="N9">
-        <v>99.859822611795806</v>
+        <v>99.979471496781912</v>
+      </c>
+      <c r="O9">
+        <v>95397.8</v>
+      </c>
+      <c r="P9">
+        <v>3906.083678059138</v>
+      </c>
+      <c r="Q9">
+        <v>88493</v>
+      </c>
+      <c r="R9">
+        <v>98156</v>
+      </c>
+      <c r="S9">
+        <v>0.97040197614624046</v>
+      </c>
+      <c r="T9">
+        <v>6.2750783015303466E-3</v>
+      </c>
+      <c r="U9">
+        <v>0.96687006909122053</v>
+      </c>
+      <c r="V9">
+        <v>0.98155994514318612</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -4938,1062 +5143,798 @@
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C10">
-        <v>1020.2</v>
-      </c>
-      <c r="D10" s="15">
-        <v>23.70021096952517</v>
+      <c r="C10" s="4">
+        <v>1140.8</v>
+      </c>
+      <c r="D10" s="10">
+        <v>30.351276744150301</v>
       </c>
       <c r="E10">
-        <v>1003</v>
-      </c>
-      <c r="F10">
-        <v>1062</v>
+        <v>1091</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1165</v>
       </c>
       <c r="G10">
-        <v>43.197508430480958</v>
+        <v>59.83351917266846</v>
       </c>
       <c r="H10">
-        <v>3.7255837028210061</v>
+        <v>2.8164001671828549</v>
       </c>
       <c r="I10">
-        <v>38.572652578353882</v>
+        <v>56.787107706069953</v>
       </c>
       <c r="J10">
-        <v>48.984535217285163</v>
+        <v>63.788259983062737</v>
       </c>
       <c r="K10">
-        <v>99.883752388793027</v>
+        <v>99.69061353592565</v>
       </c>
       <c r="L10">
-        <v>5.35086080521971E-2</v>
+        <v>0.28885796085628229</v>
       </c>
       <c r="M10">
-        <v>99.859822611795806</v>
+        <v>99.401755575069345</v>
       </c>
       <c r="N10">
-        <v>99.979471496781912</v>
-      </c>
-      <c r="O10">
-        <v>95397.8</v>
-      </c>
-      <c r="P10">
-        <v>3906.083678059138</v>
-      </c>
-      <c r="Q10">
-        <v>88493</v>
-      </c>
-      <c r="R10">
-        <v>98156</v>
-      </c>
-      <c r="S10">
-        <v>0.97040197614624046</v>
-      </c>
-      <c r="T10">
-        <v>6.2750783015303466E-3</v>
-      </c>
-      <c r="U10">
-        <v>0.96687006909122053</v>
-      </c>
-      <c r="V10">
-        <v>0.98155994514318612</v>
+        <v>99.97947149678194</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
+      <c r="A11" s="15" t="s">
+        <v>34</v>
+      </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1140.8</v>
-      </c>
-      <c r="D11" s="15">
-        <v>30.351276744150301</v>
+        <v>8</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1335</v>
       </c>
       <c r="E11">
-        <v>1091</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1165</v>
+        <v>1335</v>
+      </c>
+      <c r="F11">
+        <v>1335</v>
       </c>
       <c r="G11">
-        <v>59.83351917266846</v>
-      </c>
-      <c r="H11">
-        <v>2.8164001671828549</v>
+        <v>4.7381353378295898</v>
       </c>
       <c r="I11">
-        <v>56.787107706069953</v>
+        <v>4.7381353378295898</v>
       </c>
       <c r="J11">
-        <v>63.788259983062737</v>
+        <v>4.7381353378295898</v>
       </c>
       <c r="K11">
-        <v>99.69061353592565</v>
-      </c>
-      <c r="L11">
-        <v>0.28885796085628229</v>
+        <v>99.815513037361498</v>
       </c>
       <c r="M11">
-        <v>99.401755575069345</v>
+        <v>99.815513037361498</v>
       </c>
       <c r="N11">
-        <v>99.97947149678194</v>
+        <v>99.815513037361498</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="A12" s="15"/>
       <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="9">
-        <v>1335</v>
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>1194.8</v>
+      </c>
+      <c r="D12">
+        <v>47.73049339782694</v>
       </c>
       <c r="E12">
-        <v>1335</v>
+        <v>1115</v>
       </c>
       <c r="F12">
-        <v>1335</v>
+        <v>1231</v>
       </c>
       <c r="G12">
-        <v>4.7381353378295898</v>
+        <v>38.901602602005013</v>
+      </c>
+      <c r="H12">
+        <v>2.2528679831595189</v>
       </c>
       <c r="I12">
-        <v>4.7381353378295898</v>
+        <v>35.83539891242981</v>
       </c>
       <c r="J12">
-        <v>4.7381353378295898</v>
+        <v>41.034689664840698</v>
       </c>
       <c r="K12">
-        <v>99.815513037361498</v>
+        <v>99.670995585502823</v>
+      </c>
+      <c r="L12">
+        <v>0.25066405096359612</v>
       </c>
       <c r="M12">
-        <v>99.815513037361498</v>
+        <v>99.383233194830979</v>
       </c>
       <c r="N12">
-        <v>99.815513037361498</v>
+        <v>99.949805167498852</v>
+      </c>
+      <c r="O12">
+        <v>98723.4</v>
+      </c>
+      <c r="P12">
+        <v>764.57099081772549</v>
+      </c>
+      <c r="Q12">
+        <v>97928</v>
+      </c>
+      <c r="R12">
+        <v>99568</v>
+      </c>
+      <c r="S12">
+        <v>0.98723463025394076</v>
+      </c>
+      <c r="T12">
+        <v>7.6454653330533372E-3</v>
+      </c>
+      <c r="U12">
+        <v>0.97928081150123847</v>
+      </c>
+      <c r="V12">
+        <v>0.9956803455723543</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>1096.5999999999999</v>
+        <v>1082.4000000000001</v>
       </c>
       <c r="D13">
-        <v>8.2945765413310788</v>
+        <v>13.90323703315169</v>
       </c>
       <c r="E13">
-        <v>1087</v>
+        <v>1061</v>
       </c>
       <c r="F13">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="G13">
-        <v>31.85868577957153</v>
+        <v>8.0631880760192871</v>
       </c>
       <c r="H13">
-        <v>0.23410009834048051</v>
+        <v>0.2009896513001134</v>
       </c>
       <c r="I13">
-        <v>31.455187082290649</v>
+        <v>7.8727531433105469</v>
       </c>
       <c r="J13">
-        <v>32.062694787979133</v>
+        <v>8.3108222484588623</v>
       </c>
       <c r="K13">
-        <v>99.949805167498852</v>
+        <v>99.897624374569972</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>0.1166798001088146</v>
       </c>
       <c r="M13">
-        <v>99.949805167498852</v>
+        <v>99.688901202854453</v>
       </c>
       <c r="N13">
         <v>99.949805167498852</v>
       </c>
-      <c r="O13">
-        <v>98418.2</v>
-      </c>
-      <c r="P13">
-        <v>1936.6165598796269</v>
-      </c>
-      <c r="Q13">
-        <v>95979</v>
-      </c>
-      <c r="R13">
-        <v>99911</v>
-      </c>
-      <c r="S13">
-        <v>0.98418219762147818</v>
-      </c>
-      <c r="T13">
-        <v>1.9366055256749139E-2</v>
-      </c>
-      <c r="U13">
-        <v>0.95979068224404041</v>
-      </c>
-      <c r="V13">
-        <v>0.99911007119430451</v>
-      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>1194.8</v>
+        <v>1066.5999999999999</v>
       </c>
       <c r="D14">
-        <v>47.73049339782694</v>
+        <v>20.70748656887163</v>
       </c>
       <c r="E14">
-        <v>1115</v>
+        <v>1034</v>
       </c>
       <c r="F14">
-        <v>1231</v>
+        <v>1086</v>
       </c>
       <c r="G14">
-        <v>38.901602602005013</v>
+        <v>47.414732837677001</v>
       </c>
       <c r="H14">
-        <v>2.2528679831595189</v>
+        <v>2.375310511542168</v>
       </c>
       <c r="I14">
-        <v>35.83539891242981</v>
+        <v>43.973696947097778</v>
       </c>
       <c r="J14">
-        <v>41.034689664840698</v>
+        <v>50.431108713150017</v>
       </c>
       <c r="K14">
-        <v>99.670995585502823</v>
+        <v>99.949805167498852</v>
       </c>
       <c r="L14">
-        <v>0.25066405096359612</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>99.383233194830979</v>
+        <v>99.949805167498852</v>
       </c>
       <c r="N14">
         <v>99.949805167498852</v>
       </c>
       <c r="O14">
-        <v>98723.4</v>
+        <v>77216.399999999994</v>
       </c>
       <c r="P14">
-        <v>764.57099081772549</v>
+        <v>42973.395994498736</v>
       </c>
       <c r="Q14">
-        <v>97928</v>
+        <v>355</v>
       </c>
       <c r="R14">
-        <v>99568</v>
+        <v>97414</v>
       </c>
       <c r="S14">
-        <v>0.98723463025394076</v>
+        <v>0.77216406246842628</v>
       </c>
       <c r="T14">
-        <v>7.6454653330533372E-3</v>
+        <v>0.4297341564283873</v>
       </c>
       <c r="U14">
-        <v>0.97928081150123847</v>
+        <v>3.5497160227181829E-3</v>
       </c>
       <c r="V14">
-        <v>0.9956803455723543</v>
+        <v>0.9741402003092362</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>1082.4000000000001</v>
+        <v>12</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1223.5999999999999</v>
       </c>
       <c r="D15">
-        <v>13.90323703315169</v>
+        <v>15.50161281931654</v>
       </c>
       <c r="E15">
-        <v>1061</v>
+        <v>1208</v>
       </c>
       <c r="F15">
-        <v>1098</v>
+        <v>1246</v>
       </c>
       <c r="G15">
-        <v>8.0631880760192871</v>
+        <v>65.41713910102844</v>
       </c>
       <c r="H15">
-        <v>0.2009896513001134</v>
+        <v>2.0464230314334628</v>
       </c>
       <c r="I15">
-        <v>7.8727531433105469</v>
+        <v>63.119658946990967</v>
       </c>
       <c r="J15">
-        <v>8.3108222484588623</v>
+        <v>68.321601152420044</v>
       </c>
       <c r="K15">
-        <v>99.897624374569972</v>
+        <v>99.766404362684767</v>
       </c>
       <c r="L15">
-        <v>0.1166798001088146</v>
+        <v>0.1370021428681307</v>
       </c>
       <c r="M15">
-        <v>99.688901202854453</v>
+        <v>99.53606719884273</v>
       </c>
       <c r="N15">
-        <v>99.949805167498852</v>
+        <v>99.905041124119734</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
+      <c r="A16" s="16" t="s">
+        <v>35</v>
+      </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16">
-        <v>1066.5999999999999</v>
-      </c>
-      <c r="D16">
-        <v>20.70748656887163</v>
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1418</v>
       </c>
       <c r="E16">
-        <v>1034</v>
+        <v>1418</v>
       </c>
       <c r="F16">
-        <v>1086</v>
+        <v>1418</v>
       </c>
       <c r="G16">
-        <v>47.414732837677001</v>
-      </c>
-      <c r="H16">
-        <v>2.375310511542168</v>
+        <v>4.8826541900634766</v>
       </c>
       <c r="I16">
-        <v>43.973696947097778</v>
+        <v>4.8826541900634766</v>
       </c>
       <c r="J16">
-        <v>50.431108713150017</v>
+        <v>4.8826541900634766</v>
       </c>
       <c r="K16">
-        <v>99.949805167498852</v>
-      </c>
-      <c r="L16">
+        <v>99.402258737115403</v>
+      </c>
+      <c r="M16">
+        <v>99.402258737115403</v>
+      </c>
+      <c r="N16">
+        <v>99.402258737115403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1271.2</v>
+      </c>
+      <c r="D17" s="10">
+        <v>57.56474615595905</v>
+      </c>
+      <c r="E17">
+        <v>1172</v>
+      </c>
+      <c r="F17">
+        <v>1320</v>
+      </c>
+      <c r="G17">
+        <v>42.668295431137082</v>
+      </c>
+      <c r="H17">
+        <v>1.9112913025003111</v>
+      </c>
+      <c r="I17">
+        <v>40.414850234985352</v>
+      </c>
+      <c r="J17">
+        <v>44.920749664306641</v>
+      </c>
+      <c r="K17">
+        <v>99.702285160092586</v>
+      </c>
+      <c r="L17">
+        <v>0.18718599692217591</v>
+      </c>
+      <c r="M17">
+        <v>99.487219064345183</v>
+      </c>
+      <c r="N17">
+        <v>99.982404140098794</v>
+      </c>
+      <c r="O17">
+        <v>98747.8</v>
+      </c>
+      <c r="P17">
+        <v>622.61440715743083</v>
+      </c>
+      <c r="Q17">
+        <v>97955</v>
+      </c>
+      <c r="R17">
+        <v>99627</v>
+      </c>
+      <c r="S17">
+        <v>0.98747866185345745</v>
+      </c>
+      <c r="T17">
+        <v>6.2259978961425782E-3</v>
+      </c>
+      <c r="U17">
+        <v>0.97955066390800571</v>
+      </c>
+      <c r="V17">
+        <v>0.9962702983761299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>1143</v>
+      </c>
+      <c r="D18">
+        <v>8.755950357709164</v>
+      </c>
+      <c r="E18">
+        <v>1135</v>
+      </c>
+      <c r="F18">
+        <v>1152</v>
+      </c>
+      <c r="G18">
+        <v>8.7277367115020752</v>
+      </c>
+      <c r="H18">
+        <v>0.13632354843787439</v>
+      </c>
+      <c r="I18">
+        <v>8.6101114749908447</v>
+      </c>
+      <c r="J18">
+        <v>8.8771059513092041</v>
+      </c>
+      <c r="K18">
+        <v>99.77729176583685</v>
+      </c>
+      <c r="L18">
         <v>0</v>
       </c>
-      <c r="M16">
-        <v>99.949805167498852</v>
-      </c>
-      <c r="N16">
-        <v>99.949805167498852</v>
-      </c>
-      <c r="O16">
-        <v>77216.399999999994</v>
-      </c>
-      <c r="P16">
-        <v>42973.395994498736</v>
-      </c>
-      <c r="Q16">
-        <v>355</v>
-      </c>
-      <c r="R16">
-        <v>97414</v>
-      </c>
-      <c r="S16">
-        <v>0.77216406246842628</v>
-      </c>
-      <c r="T16">
-        <v>0.4297341564283873</v>
-      </c>
-      <c r="U16">
-        <v>3.5497160227181829E-3</v>
-      </c>
-      <c r="V16">
-        <v>0.9741402003092362</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1223.5999999999999</v>
-      </c>
-      <c r="D17">
-        <v>15.50161281931654</v>
-      </c>
-      <c r="E17">
-        <v>1208</v>
-      </c>
-      <c r="F17">
-        <v>1246</v>
-      </c>
-      <c r="G17">
-        <v>65.41713910102844</v>
-      </c>
-      <c r="H17">
-        <v>2.0464230314334628</v>
-      </c>
-      <c r="I17">
-        <v>63.119658946990967</v>
-      </c>
-      <c r="J17">
-        <v>68.321601152420044</v>
-      </c>
-      <c r="K17">
-        <v>99.766404362684767</v>
-      </c>
-      <c r="L17">
-        <v>0.1370021428681307</v>
-      </c>
-      <c r="M17">
-        <v>99.53606719884273</v>
-      </c>
-      <c r="N17">
-        <v>99.905041124119734</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1418</v>
-      </c>
-      <c r="E18">
-        <v>1418</v>
-      </c>
-      <c r="F18">
-        <v>1418</v>
-      </c>
-      <c r="G18">
-        <v>4.8826541900634766</v>
-      </c>
-      <c r="I18">
-        <v>4.8826541900634766</v>
-      </c>
-      <c r="J18">
-        <v>4.8826541900634766</v>
-      </c>
-      <c r="K18">
-        <v>99.402258737115403</v>
-      </c>
       <c r="M18">
-        <v>99.402258737115403</v>
+        <v>99.77729176583685</v>
       </c>
       <c r="N18">
-        <v>99.402258737115403</v>
+        <v>99.77729176583685</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>1149</v>
+        <v>1142.75</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>18.154430129677269</v>
       </c>
       <c r="E19">
-        <v>1139</v>
+        <v>1116</v>
       </c>
       <c r="F19">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="G19">
-        <v>35.605374336242683</v>
+        <v>51.470862030982971</v>
       </c>
       <c r="H19">
-        <v>2.7153854298893179</v>
+        <v>5.6862766225305572</v>
       </c>
       <c r="I19">
-        <v>33.983964443206787</v>
+        <v>46.115494012832642</v>
       </c>
       <c r="J19">
-        <v>38.740211486816413</v>
+        <v>59.478431701660163</v>
       </c>
       <c r="K19">
-        <v>99.777291765836864</v>
+        <v>99.77729176583685</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.6409281590473081E-14</v>
       </c>
       <c r="M19">
         <v>99.77729176583685</v>
       </c>
       <c r="N19">
-        <v>99.77729176583685</v>
+        <v>99.777291765836878</v>
       </c>
       <c r="O19">
-        <v>98984</v>
+        <v>95121.5</v>
       </c>
       <c r="P19">
-        <v>1223.2072596252849</v>
+        <v>4188.8687812662092</v>
       </c>
       <c r="Q19">
-        <v>97590</v>
+        <v>88868</v>
       </c>
       <c r="R19">
-        <v>99878</v>
+        <v>97736</v>
       </c>
       <c r="S19">
-        <v>0.98984030235539466</v>
+        <v>0.97093482240389117</v>
       </c>
       <c r="T19">
-        <v>1.223180667315826E-2</v>
+        <v>4.6551928503634991E-3</v>
       </c>
       <c r="U19">
-        <v>0.97590059949890196</v>
+        <v>0.96744999149618016</v>
       </c>
       <c r="V19">
-        <v>0.9987800795929126</v>
+        <v>0.9773601083232194</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1271.2</v>
-      </c>
-      <c r="D20" s="15">
-        <v>57.56474615595905</v>
+        <v>12</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1273.4000000000001</v>
+      </c>
+      <c r="D20" s="10">
+        <v>32.439173848912979</v>
       </c>
       <c r="E20">
-        <v>1172</v>
+        <v>1229</v>
       </c>
       <c r="F20">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="G20">
-        <v>42.668295431137082</v>
+        <v>68.339952564239496</v>
       </c>
       <c r="H20">
-        <v>1.9112913025003111</v>
+        <v>4.0518669270645136</v>
       </c>
       <c r="I20">
-        <v>40.414850234985352</v>
+        <v>63.055685043334961</v>
       </c>
       <c r="J20">
-        <v>44.920749664306641</v>
+        <v>74.072880029678345</v>
       </c>
       <c r="K20">
-        <v>99.702285160092586</v>
+        <v>99.731292430241737</v>
       </c>
       <c r="L20">
-        <v>0.18718599692217591</v>
+        <v>0.15378395626041411</v>
       </c>
       <c r="M20">
-        <v>99.487219064345183</v>
+        <v>99.529699227960037</v>
       </c>
       <c r="N20">
-        <v>99.982404140098794</v>
-      </c>
-      <c r="O20">
-        <v>98747.8</v>
-      </c>
-      <c r="P20">
-        <v>622.61440715743083</v>
-      </c>
-      <c r="Q20">
-        <v>97955</v>
-      </c>
-      <c r="R20">
-        <v>99627</v>
-      </c>
-      <c r="S20">
-        <v>0.98747866185345745</v>
-      </c>
-      <c r="T20">
-        <v>6.2259978961425782E-3</v>
-      </c>
-      <c r="U20">
-        <v>0.97955066390800571</v>
-      </c>
-      <c r="V20">
-        <v>0.9962702983761299</v>
+        <v>99.879847952967822</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
+      <c r="A21" s="16" t="s">
+        <v>36</v>
+      </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21">
-        <v>1143</v>
-      </c>
-      <c r="D21">
-        <v>8.755950357709164</v>
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1546</v>
       </c>
       <c r="E21">
-        <v>1135</v>
+        <v>1546</v>
       </c>
       <c r="F21">
-        <v>1152</v>
+        <v>1546</v>
       </c>
       <c r="G21">
-        <v>8.7277367115020752</v>
-      </c>
-      <c r="H21">
-        <v>0.13632354843787439</v>
+        <v>6.4800376892089844</v>
       </c>
       <c r="I21">
-        <v>8.6101114749908447</v>
+        <v>6.4800376892089844</v>
       </c>
       <c r="J21">
-        <v>8.8771059513092041</v>
+        <v>6.4800376892089844</v>
       </c>
       <c r="K21">
-        <v>99.77729176583685</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>99.77729176583685</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>99.77729176583685</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22">
-        <v>1142.75</v>
+        <v>9</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1378.2</v>
       </c>
       <c r="D22">
-        <v>18.154430129677269</v>
+        <v>88.03238040630275</v>
       </c>
       <c r="E22">
-        <v>1116</v>
+        <v>1231</v>
       </c>
       <c r="F22">
-        <v>1155</v>
+        <v>1463</v>
       </c>
       <c r="G22">
-        <v>51.470862030982971</v>
+        <v>46.536655569076537</v>
       </c>
       <c r="H22">
-        <v>5.6862766225305572</v>
+        <v>5.1004126978293867</v>
       </c>
       <c r="I22">
-        <v>46.115494012832642</v>
+        <v>39.030210494995117</v>
       </c>
       <c r="J22">
-        <v>59.478431701660163</v>
+        <v>51.42918586730957</v>
       </c>
       <c r="K22">
-        <v>99.77729176583685</v>
+        <v>99.664793468652263</v>
       </c>
       <c r="L22">
-        <v>1.6409281590473081E-14</v>
+        <v>0.1998297017696288</v>
       </c>
       <c r="M22">
-        <v>99.77729176583685</v>
+        <v>99.460192480781245</v>
       </c>
       <c r="N22">
-        <v>99.777291765836878</v>
+        <v>99.943389900917552</v>
       </c>
       <c r="O22">
-        <v>95121.5</v>
+        <v>98475.4</v>
       </c>
       <c r="P22">
-        <v>4188.8687812662092</v>
+        <v>742.62561227040715</v>
       </c>
       <c r="Q22">
-        <v>88868</v>
+        <v>97739</v>
       </c>
       <c r="R22">
-        <v>97736</v>
+        <v>99396</v>
       </c>
       <c r="S22">
-        <v>0.97093482240389117</v>
+        <v>0.98475482263830982</v>
       </c>
       <c r="T22">
-        <v>4.6551928503634991E-3</v>
+        <v>7.4260217297375522E-3</v>
       </c>
       <c r="U22">
-        <v>0.96744999149618016</v>
+        <v>0.97739105268554394</v>
       </c>
       <c r="V22">
-        <v>0.9773601083232194</v>
+        <v>0.993960483161347</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1273.4000000000001</v>
-      </c>
-      <c r="D23" s="15">
-        <v>32.439173848912979</v>
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>1250</v>
       </c>
       <c r="E23">
-        <v>1229</v>
+        <v>1250</v>
       </c>
       <c r="F23">
-        <v>1319</v>
+        <v>1250</v>
       </c>
       <c r="G23">
-        <v>68.339952564239496</v>
-      </c>
-      <c r="H23">
-        <v>4.0518669270645136</v>
+        <v>9.8094737529754639</v>
       </c>
       <c r="I23">
-        <v>63.055685043334961</v>
+        <v>9.8094737529754639</v>
       </c>
       <c r="J23">
-        <v>74.072880029678345</v>
+        <v>9.8094737529754639</v>
       </c>
       <c r="K23">
-        <v>99.731292430241737</v>
-      </c>
-      <c r="L23">
-        <v>0.15378395626041411</v>
+        <v>99.790140317807797</v>
       </c>
       <c r="M23">
-        <v>99.529699227960037</v>
+        <v>99.790140317807797</v>
       </c>
       <c r="N23">
-        <v>99.879847952967822</v>
+        <v>99.790140317807797</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>38</v>
-      </c>
+      <c r="A24" s="16"/>
       <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="9">
-        <v>1546</v>
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>1265</v>
+      </c>
+      <c r="D24">
+        <v>2.8284271247461898</v>
       </c>
       <c r="E24">
-        <v>1546</v>
+        <v>1263</v>
       </c>
       <c r="F24">
-        <v>1546</v>
+        <v>1267</v>
       </c>
       <c r="G24">
-        <v>6.4800376892089844</v>
+        <v>54.135406494140618</v>
+      </c>
+      <c r="H24">
+        <v>0.74503961919592832</v>
       </c>
       <c r="I24">
-        <v>6.4800376892089844</v>
+        <v>53.608583927154541</v>
       </c>
       <c r="J24">
-        <v>6.4800376892089844</v>
+        <v>54.662229061126709</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>99.790140317807811</v>
+      </c>
+      <c r="L24">
+        <v>1.4210854715202001E-14</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>99.790140317807797</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>99.790140317807811</v>
+      </c>
+      <c r="O24">
+        <v>48818</v>
+      </c>
+      <c r="P24">
+        <v>67832.753519225502</v>
+      </c>
+      <c r="Q24">
+        <v>853</v>
+      </c>
+      <c r="R24">
+        <v>96783</v>
+      </c>
+      <c r="S24">
+        <v>0.48817962497717571</v>
+      </c>
+      <c r="T24">
+        <v>0.67832795623611997</v>
+      </c>
+      <c r="U24">
+        <v>8.5293272542036804E-3</v>
+      </c>
+      <c r="V24">
+        <v>0.96782992270014778</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>1243</v>
+        <v>1369</v>
       </c>
       <c r="D25">
-        <v>12.727922061357861</v>
+        <v>18.124568960391858</v>
       </c>
       <c r="E25">
-        <v>1234</v>
+        <v>1342</v>
       </c>
       <c r="F25">
-        <v>1252</v>
+        <v>1393</v>
       </c>
       <c r="G25">
-        <v>37.030025124549873</v>
+        <v>75.366956233978271</v>
       </c>
       <c r="H25">
-        <v>0.53104337915410904</v>
+        <v>2.7862316097811921</v>
       </c>
       <c r="I25">
-        <v>36.654520750045783</v>
+        <v>72.624467849731445</v>
       </c>
       <c r="J25">
-        <v>37.405529499053962</v>
+        <v>79.942618608474731</v>
       </c>
       <c r="K25">
-        <v>99.790140317807811</v>
+        <v>99.793456460635355</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>0.1449118049377007</v>
       </c>
       <c r="M25">
-        <v>99.790140317807797</v>
+        <v>99.556831964808509</v>
       </c>
       <c r="N25">
-        <v>99.790140317807811</v>
-      </c>
-      <c r="O25">
-        <v>99833</v>
-      </c>
-      <c r="P25">
-        <v>41.012193308819747</v>
-      </c>
-      <c r="Q25">
-        <v>99804</v>
-      </c>
-      <c r="R25">
-        <v>99862</v>
-      </c>
-      <c r="S25">
-        <v>0.99833011199017674</v>
-      </c>
-      <c r="T25">
-        <v>4.1011797476093261E-4</v>
-      </c>
-      <c r="U25">
-        <v>0.99804011478913679</v>
-      </c>
-      <c r="V25">
-        <v>0.99862010919121669</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>1378.2</v>
-      </c>
-      <c r="D26">
-        <v>88.03238040630275</v>
-      </c>
-      <c r="E26">
-        <v>1231</v>
-      </c>
-      <c r="F26">
-        <v>1463</v>
-      </c>
-      <c r="G26">
-        <v>46.536655569076537</v>
-      </c>
-      <c r="H26">
-        <v>5.1004126978293867</v>
-      </c>
-      <c r="I26">
-        <v>39.030210494995117</v>
-      </c>
-      <c r="J26">
-        <v>51.42918586730957</v>
-      </c>
-      <c r="K26">
-        <v>99.664793468652263</v>
-      </c>
-      <c r="L26">
-        <v>0.1998297017696288</v>
-      </c>
-      <c r="M26">
-        <v>99.460192480781245</v>
-      </c>
-      <c r="N26">
-        <v>99.943389900917552</v>
-      </c>
-      <c r="O26">
-        <v>98475.4</v>
-      </c>
-      <c r="P26">
-        <v>742.62561227040715</v>
-      </c>
-      <c r="Q26">
-        <v>97739</v>
-      </c>
-      <c r="R26">
-        <v>99396</v>
-      </c>
-      <c r="S26">
-        <v>0.98475482263830982</v>
-      </c>
-      <c r="T26">
-        <v>7.4260217297375522E-3</v>
-      </c>
-      <c r="U26">
-        <v>0.97739105268554394</v>
-      </c>
-      <c r="V26">
-        <v>0.993960483161347</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27">
-        <v>1250</v>
-      </c>
-      <c r="E27">
-        <v>1250</v>
-      </c>
-      <c r="F27">
-        <v>1250</v>
-      </c>
-      <c r="G27">
-        <v>9.8094737529754639</v>
-      </c>
-      <c r="I27">
-        <v>9.8094737529754639</v>
-      </c>
-      <c r="J27">
-        <v>9.8094737529754639</v>
-      </c>
-      <c r="K27">
-        <v>99.790140317807797</v>
-      </c>
-      <c r="M27">
-        <v>99.790140317807797</v>
-      </c>
-      <c r="N27">
-        <v>99.790140317807797</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28">
-        <v>1265</v>
-      </c>
-      <c r="D28">
-        <v>2.8284271247461898</v>
-      </c>
-      <c r="E28">
-        <v>1263</v>
-      </c>
-      <c r="F28">
-        <v>1267</v>
-      </c>
-      <c r="G28">
-        <v>54.135406494140618</v>
-      </c>
-      <c r="H28">
-        <v>0.74503961919592832</v>
-      </c>
-      <c r="I28">
-        <v>53.608583927154541</v>
-      </c>
-      <c r="J28">
-        <v>54.662229061126709</v>
-      </c>
-      <c r="K28">
-        <v>99.790140317807811</v>
-      </c>
-      <c r="L28">
-        <v>1.4210854715202001E-14</v>
-      </c>
-      <c r="M28">
-        <v>99.790140317807797</v>
-      </c>
-      <c r="N28">
-        <v>99.790140317807811</v>
-      </c>
-      <c r="O28">
-        <v>48818</v>
-      </c>
-      <c r="P28">
-        <v>67832.753519225502</v>
-      </c>
-      <c r="Q28">
-        <v>853</v>
-      </c>
-      <c r="R28">
-        <v>96783</v>
-      </c>
-      <c r="S28">
-        <v>0.48817962497717571</v>
-      </c>
-      <c r="T28">
-        <v>0.67832795623611997</v>
-      </c>
-      <c r="U28">
-        <v>8.5293272542036804E-3</v>
-      </c>
-      <c r="V28">
-        <v>0.96782992270014778</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29">
-        <v>1369</v>
-      </c>
-      <c r="D29">
-        <v>18.124568960391858</v>
-      </c>
-      <c r="E29">
-        <v>1342</v>
-      </c>
-      <c r="F29">
-        <v>1393</v>
-      </c>
-      <c r="G29">
-        <v>75.366956233978271</v>
-      </c>
-      <c r="H29">
-        <v>2.7862316097811921</v>
-      </c>
-      <c r="I29">
-        <v>72.624467849731445</v>
-      </c>
-      <c r="J29">
-        <v>79.942618608474731</v>
-      </c>
-      <c r="K29">
-        <v>99.793456460635355</v>
-      </c>
-      <c r="L29">
-        <v>0.1449118049377007</v>
-      </c>
-      <c r="M29">
-        <v>99.556831964808509</v>
-      </c>
-      <c r="N29">
         <v>99.886779801835075</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="O3:R3"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results_gen/outputs/Test_all.xlsx
+++ b/results_gen/outputs/Test_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reube\Parallel-Monte-Carlo-Tree-Search-For-The-Orienteering-Problem\results_gen\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/reubenkappely/Documents/Projects/Parallel-Monte-Carlo-Tree-Search-For-The-Orienteering-Problem/results_gen/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5351F0F-73B9-4227-89EA-B500E874AF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E99C3C2-967D-CD46-AE8E-616D3C4C354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-45" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{260B2045-1352-43BA-9B1E-29C2A8BE3BD5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{260B2045-1352-43BA-9B1E-29C2A8BE3BD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Test1" sheetId="1" r:id="rId1"/>
@@ -168,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +223,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -274,7 +281,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -334,11 +341,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -359,10 +397,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -371,16 +406,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -398,9 +433,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,50 +778,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2055FE3-E712-4367-9B42-B5E3B258A2F1}">
   <dimension ref="A1:V55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41.5703125" customWidth="1"/>
+    <col min="1" max="1" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -842,7 +884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -850,8 +892,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -867,8 +909,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,8 +927,8 @@
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -903,8 +945,8 @@
         <v>388</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -921,8 +963,8 @@
         <v>358</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -939,8 +981,8 @@
         <v>395</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -956,8 +998,8 @@
         <v>558</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="15"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -974,8 +1016,8 @@
         <v>526</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -992,8 +1034,8 @@
         <v>509</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1010,8 +1052,8 @@
         <v>499</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1028,8 +1070,8 @@
         <v>501</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1045,8 +1087,8 @@
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="21"/>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,8 +1105,8 @@
         <v>350</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="21"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -1081,8 +1123,8 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="21"/>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,8 +1144,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="21"/>
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
@@ -1120,8 +1162,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1137,8 +1179,8 @@
         <v>444</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="21"/>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
@@ -1155,8 +1197,8 @@
         <v>479</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="22"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="21"/>
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -1173,8 +1215,8 @@
         <v>451</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -1191,8 +1233,8 @@
         <v>454</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="22"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="21"/>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -1209,14 +1251,14 @@
         <v>469</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="20" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="2">
         <v>453</v>
       </c>
       <c r="E26">
@@ -1226,8 +1268,8 @@
         <v>453</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="20"/>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
@@ -1244,8 +1286,8 @@
         <v>486</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="20"/>
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
@@ -1265,8 +1307,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="20"/>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -1283,8 +1325,8 @@
         <v>465</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="20"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
@@ -1301,8 +1343,8 @@
         <v>480</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1318,8 +1360,8 @@
         <v>622</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="15"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -1336,8 +1378,8 @@
         <v>643</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A33" s="15"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -1354,8 +1396,8 @@
         <v>606</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" s="15"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1372,8 +1414,8 @@
         <v>602</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" s="15"/>
       <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
@@ -1390,8 +1432,8 @@
         <v>653</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -1407,8 +1449,8 @@
         <v>414</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" s="15"/>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
@@ -1425,8 +1467,8 @@
         <v>380</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" s="15"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -1443,15 +1485,15 @@
         <v>390</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" s="15"/>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C39">
         <v>321</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="29">
         <v>50.383529054642452</v>
       </c>
       <c r="E39">
@@ -1461,15 +1503,15 @@
         <v>390</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" s="15"/>
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C40">
         <v>308</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="29">
         <v>51.112620750652177</v>
       </c>
       <c r="E40">
@@ -1479,8 +1521,8 @@
         <v>392</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" s="15" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -1496,8 +1538,8 @@
         <v>536</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" s="15"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -1514,8 +1556,8 @@
         <v>494</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" s="15"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -1532,8 +1574,8 @@
         <v>495</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" s="15"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -1550,8 +1592,8 @@
         <v>475</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A45" s="15"/>
       <c r="B45" s="1" t="s">
         <v>12</v>
       </c>
@@ -1568,14 +1610,14 @@
         <v>497</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" s="26" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="5">
         <v>303</v>
       </c>
       <c r="E46">
@@ -1603,9 +1645,9 @@
         <v>99.621165057908925</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47" s="18"/>
-      <c r="B47" s="27" t="s">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" s="27"/>
+      <c r="B47" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C47">
@@ -1669,8 +1711,8 @@
         <v>0.97419999999999995</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A48" s="18"/>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" s="27"/>
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
@@ -1711,8 +1753,8 @@
         <v>99.329966244077795</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="19"/>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A49" s="27"/>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -1777,10 +1819,8 @@
         <v>0.54720000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>28</v>
-      </c>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A50" s="28"/>
       <c r="B50" s="1" t="s">
         <v>12</v>
       </c>
@@ -1821,12 +1861,14 @@
         <v>99.66498312203889</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="20"/>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A51" s="26" t="s">
+        <v>28</v>
+      </c>
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="5">
         <v>348</v>
       </c>
       <c r="E51">
@@ -1854,12 +1896,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="20"/>
-      <c r="B52" s="27" t="s">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A52" s="27"/>
+      <c r="B52" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="4">
         <v>443.6</v>
       </c>
       <c r="D52">
@@ -1920,8 +1962,8 @@
         <v>0.9829</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="21"/>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A53" s="27"/>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
@@ -1962,7 +2004,8 @@
         <v>99.497474683058343</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A54" s="27"/>
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -2027,7 +2070,8 @@
         <v>0.69609999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A55" s="27"/>
       <c r="B55" s="1" t="s">
         <v>12</v>
       </c>
@@ -2070,11 +2114,7 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A36:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="A51:A55"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="O3:R3"/>
@@ -2085,6 +2125,10 @@
     <mergeCell ref="A11:A15"/>
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="A21:A25"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A36:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2093,51 +2137,51 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B9F7C1-6CD3-4B61-9368-31485E040906}">
   <dimension ref="A1:V55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -2200,7 +2244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2208,8 +2252,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2225,8 +2269,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -2243,8 +2287,8 @@
         <v>402</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -2261,8 +2305,8 @@
         <v>379</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -2279,8 +2323,8 @@
         <v>417</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -2297,8 +2341,8 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2314,8 +2358,8 @@
         <v>558</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="15"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -2335,8 +2379,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -2353,8 +2397,8 @@
         <v>503</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -2371,12 +2415,12 @@
         <v>492</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>498.4</v>
       </c>
       <c r="D15">
@@ -2389,8 +2433,8 @@
         <v>518</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -2406,8 +2450,8 @@
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="21"/>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
@@ -2424,8 +2468,8 @@
         <v>352</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="21"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -2442,8 +2486,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="21"/>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -2460,8 +2504,8 @@
         <v>339</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="25"/>
       <c r="B20" s="8" t="s">
         <v>12</v>
       </c>
@@ -2478,8 +2522,8 @@
         <v>345</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -2495,8 +2539,8 @@
         <v>444</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="17"/>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
@@ -2513,8 +2557,8 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="17"/>
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -2531,8 +2575,8 @@
         <v>453</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="20"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="17"/>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -2549,8 +2593,8 @@
         <v>416</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="18"/>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -2567,8 +2611,8 @@
         <v>481</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2584,8 +2628,8 @@
         <v>453</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="20"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="17"/>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
@@ -2605,8 +2649,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="17"/>
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
@@ -2623,8 +2667,8 @@
         <v>481</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="17"/>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -2641,8 +2685,8 @@
         <v>495</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="18"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
@@ -2659,8 +2703,8 @@
         <v>510</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2676,8 +2720,8 @@
         <v>622</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="23"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -2694,8 +2738,8 @@
         <v>608</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A33" s="23"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -2712,8 +2756,8 @@
         <v>610</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" s="23"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -2730,12 +2774,12 @@
         <v>625</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" s="24"/>
       <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="3">
         <v>592</v>
       </c>
       <c r="D35">
@@ -2748,8 +2792,8 @@
         <v>643</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" s="22" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2765,8 +2809,8 @@
         <v>414</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" s="23"/>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
@@ -2786,8 +2830,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" s="23"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -2804,8 +2848,8 @@
         <v>358</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" s="23"/>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -2822,8 +2866,8 @@
         <v>378</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" s="24"/>
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
@@ -2840,8 +2884,8 @@
         <v>309</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" s="22" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -2857,8 +2901,8 @@
         <v>536</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" s="23"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -2875,8 +2919,8 @@
         <v>497</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" s="23"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -2896,8 +2940,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" s="23"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -2914,8 +2958,8 @@
         <v>432</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A45" s="24"/>
       <c r="B45" s="1" t="s">
         <v>12</v>
       </c>
@@ -2932,8 +2976,8 @@
         <v>454</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2967,8 +3011,8 @@
         <v>99.621165057908925</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47" s="20"/>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" s="17"/>
       <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
@@ -3033,8 +3077,8 @@
         <v>0.98160000000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A48" s="20"/>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" s="17"/>
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
@@ -3075,8 +3119,8 @@
         <v>99.329966244077795</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A49" s="17"/>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -3141,8 +3185,8 @@
         <v>0.89880000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="21"/>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A50" s="18"/>
       <c r="B50" s="1" t="s">
         <v>12</v>
       </c>
@@ -3183,8 +3227,8 @@
         <v>99.66498312203889</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A51" s="16" t="s">
         <v>28</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -3218,8 +3262,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="20"/>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A52" s="17"/>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
@@ -3284,8 +3328,8 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="20"/>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A53" s="17"/>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
@@ -3326,8 +3370,8 @@
         <v>99.497474683058343</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A54" s="20"/>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A54" s="17"/>
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -3392,8 +3436,8 @@
         <v>0.89949999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A55" s="21"/>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A55" s="18"/>
       <c r="B55" s="1" t="s">
         <v>12</v>
       </c>
@@ -3459,51 +3503,51 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58126609-257A-4A45-B385-DFB3BFE448A7}">
   <dimension ref="A1:V55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -3566,7 +3610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -3574,8 +3618,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -3591,8 +3635,8 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="21"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -3609,8 +3653,8 @@
         <v>398</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="21"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3627,8 +3671,8 @@
         <v>393</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="21"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -3645,8 +3689,8 @@
         <v>392</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="21"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -3663,8 +3707,8 @@
         <v>401</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -3680,8 +3724,8 @@
         <v>558</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="15"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -3698,8 +3742,8 @@
         <v>534</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3716,8 +3760,8 @@
         <v>496</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -3734,8 +3778,8 @@
         <v>508</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3752,8 +3796,8 @@
         <v>518</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -3769,8 +3813,8 @@
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="21"/>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
@@ -3787,8 +3831,8 @@
         <v>350</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="21"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -3808,8 +3852,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="21"/>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -3826,8 +3870,8 @@
         <v>354</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="21"/>
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
@@ -3844,8 +3888,8 @@
         <v>353</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="21" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -3861,8 +3905,8 @@
         <v>444</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="21"/>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
@@ -3879,8 +3923,8 @@
         <v>463</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="22"/>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="21"/>
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -3897,8 +3941,8 @@
         <v>451</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -3915,8 +3959,8 @@
         <v>401</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="22"/>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="21"/>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -3933,8 +3977,8 @@
         <v>434</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="20" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -3950,8 +3994,8 @@
         <v>453</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="20"/>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
@@ -3968,8 +4012,8 @@
         <v>515</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="20"/>
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
@@ -3986,8 +4030,8 @@
         <v>477</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="20"/>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -4004,8 +4048,8 @@
         <v>475</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="20"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
@@ -4022,8 +4066,8 @@
         <v>535</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -4039,8 +4083,8 @@
         <v>622</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="15"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -4057,8 +4101,8 @@
         <v>615</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A33" s="15"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -4075,8 +4119,8 @@
         <v>598</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" s="15"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -4093,8 +4137,8 @@
         <v>584</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" s="15"/>
       <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
@@ -4111,8 +4155,8 @@
         <v>620</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -4128,8 +4172,8 @@
         <v>414</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" s="15"/>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
@@ -4146,8 +4190,8 @@
         <v>397</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A38" s="16"/>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" s="15"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -4164,8 +4208,8 @@
         <v>383</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A39" s="16"/>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" s="15"/>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -4182,8 +4226,8 @@
         <v>362</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" s="15"/>
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
@@ -4200,8 +4244,8 @@
         <v>379</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" s="15" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -4217,8 +4261,8 @@
         <v>536</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" s="15"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -4235,8 +4279,8 @@
         <v>483</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A43" s="16"/>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" s="15"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -4253,8 +4297,8 @@
         <v>476</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A44" s="16"/>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" s="15"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -4271,8 +4315,8 @@
         <v>479</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A45" s="15"/>
       <c r="B45" s="1" t="s">
         <v>12</v>
       </c>
@@ -4289,8 +4333,8 @@
         <v>463</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" s="20" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -4324,9 +4368,9 @@
         <v>99.621165057908925</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="27" t="s">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" s="20"/>
+      <c r="B47" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C47">
@@ -4390,8 +4434,8 @@
         <v>0.99695999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" s="20"/>
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
@@ -4432,8 +4476,8 @@
         <v>99.66498312203889</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A49" s="20"/>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -4498,8 +4542,8 @@
         <v>0.89973999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="15" t="s">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A50" s="20" t="s">
         <v>28</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -4542,8 +4586,8 @@
         <v>99.66498312203889</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A51" s="20"/>
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
@@ -4575,9 +4619,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="15"/>
-      <c r="B52" s="27" t="s">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A52" s="20"/>
+      <c r="B52" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C52">
@@ -4641,8 +4685,8 @@
         <v>0.98977999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A53" s="20"/>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
@@ -4683,7 +4727,7 @@
         <v>99.497474683058343</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -4748,7 +4792,7 @@
         <v>0.87141999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B55" s="1" t="s">
         <v>12</v>
       </c>
@@ -4791,6 +4835,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A36:A40"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A53"/>
@@ -4801,11 +4850,6 @@
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="A26:A30"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A36:A40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4814,51 +4858,51 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986CE34A-0472-4CC3-8683-488EBE5AEA7F}">
   <dimension ref="A1:V25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14" t="s">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14" t="s">
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -4921,7 +4965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -4929,8 +4973,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -4964,8 +5008,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="15"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -5030,8 +5074,8 @@
         <v>0.99913006959443251</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="15"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -5072,8 +5116,8 @@
         <v>99.859822611795806</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="15"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -5138,8 +5182,8 @@
         <v>0.98155994514318612</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="15"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -5180,8 +5224,8 @@
         <v>99.97947149678194</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -5215,8 +5259,8 @@
         <v>99.815513037361498</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -5281,8 +5325,8 @@
         <v>0.9956803455723543</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -5323,8 +5367,8 @@
         <v>99.949805167498852</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="20"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -5389,8 +5433,8 @@
         <v>0.9741402003092362</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="20"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -5431,8 +5475,8 @@
         <v>99.905041124119734</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5466,8 +5510,8 @@
         <v>99.402258737115403</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17" s="15"/>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
@@ -5532,8 +5576,8 @@
         <v>0.9962702983761299</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" s="15"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -5574,8 +5618,8 @@
         <v>99.77729176583685</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A19" s="15"/>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -5640,12 +5684,12 @@
         <v>0.9773601083232194</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A20" s="15"/>
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>1273.4000000000001</v>
       </c>
       <c r="D20" s="10">
@@ -5682,8 +5726,8 @@
         <v>99.879847952967822</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A21" s="15" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -5717,8 +5761,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A22" s="15"/>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
@@ -5783,8 +5827,8 @@
         <v>0.993960483161347</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A23" s="15"/>
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -5816,8 +5860,8 @@
         <v>99.790140317807797</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A24" s="15"/>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -5882,8 +5926,8 @@
         <v>0.96782992270014778</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A25" s="15"/>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -5926,15 +5970,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="A6:A10"/>
     <mergeCell ref="A11:A15"/>
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:N3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results_gen/outputs/Test_all.xlsx
+++ b/results_gen/outputs/Test_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/reubenkappely/Documents/Projects/Parallel-Monte-Carlo-Tree-Search-For-The-Orienteering-Problem/results_gen/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E99C3C2-967D-CD46-AE8E-616D3C4C354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428D37E0-9E8C-1C4A-AA9C-2E0B5160DF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{260B2045-1352-43BA-9B1E-29C2A8BE3BD5}"/>
   </bookViews>
@@ -222,6 +222,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -400,7 +401,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -410,15 +430,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -433,16 +444,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -777,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2055FE3-E712-4367-9B42-B5E3B258A2F1}">
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.5" customWidth="1"/>
@@ -790,36 +791,36 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19" t="s">
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
@@ -893,7 +894,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -910,7 +911,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,7 +929,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -946,7 +947,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -964,7 +965,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -982,7 +983,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="20" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -999,7 +1000,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="15"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1017,7 +1018,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1035,7 +1036,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="15"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1053,7 +1054,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
+      <c r="A15" s="20"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1252,7 +1253,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1269,7 +1270,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
@@ -1287,7 +1288,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
@@ -1308,7 +1309,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -1326,7 +1327,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
@@ -1344,7 +1345,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1361,7 +1362,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
+      <c r="A32" s="20"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,7 +1380,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,7 +1398,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
+      <c r="A34" s="20"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
+      <c r="A35" s="20"/>
       <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
@@ -1433,7 +1434,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="20" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -1450,7 +1451,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
+      <c r="A37" s="20"/>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
@@ -1468,7 +1469,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
+      <c r="A38" s="20"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -1486,14 +1487,14 @@
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="15"/>
+      <c r="A39" s="20"/>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C39">
         <v>321</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="15">
         <v>50.383529054642452</v>
       </c>
       <c r="E39">
@@ -1504,14 +1505,14 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
+      <c r="A40" s="20"/>
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C40">
         <v>308</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="15">
         <v>51.112620750652177</v>
       </c>
       <c r="E40">
@@ -1522,7 +1523,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -1539,7 +1540,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A42" s="15"/>
+      <c r="A42" s="20"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -1557,7 +1558,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
+      <c r="A43" s="20"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -1575,7 +1576,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A44" s="15"/>
+      <c r="A44" s="20"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -1593,7 +1594,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
+      <c r="A45" s="20"/>
       <c r="B45" s="1" t="s">
         <v>12</v>
       </c>
@@ -1611,7 +1612,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -1646,7 +1647,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A47" s="27"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="14" t="s">
         <v>9</v>
       </c>
@@ -1712,7 +1713,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A48" s="27"/>
+      <c r="A48" s="17"/>
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
@@ -1754,7 +1755,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A49" s="27"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -1820,7 +1821,7 @@
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
+      <c r="A50" s="22"/>
       <c r="B50" s="1" t="s">
         <v>12</v>
       </c>
@@ -1862,7 +1863,7 @@
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="16" t="s">
         <v>28</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -1897,7 +1898,7 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A52" s="27"/>
+      <c r="A52" s="17"/>
       <c r="B52" s="14" t="s">
         <v>9</v>
       </c>
@@ -1963,7 +1964,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A53" s="27"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
@@ -2005,7 +2006,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A54" s="27"/>
+      <c r="A54" s="17"/>
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -2071,7 +2072,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A55" s="27"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="1" t="s">
         <v>12</v>
       </c>
@@ -2110,6 +2111,102 @@
       </c>
       <c r="N55">
         <v>99.748737341529164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <f>Test2!C10/Test1!C10</f>
+        <v>1.0143516145566376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <f>(Test2!C50-Test1!C50)/Test1!C50*100</f>
+        <v>1.392757660167131</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <f>(Test2!C55-Test1!C55)/Test1!C55*100</f>
+        <v>1.8148820326678767</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63">
+        <f>(Test2!C10-C10)/C10*100</f>
+        <v>1.4351614556637682</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="C64">
+        <v>4</v>
+      </c>
+      <c r="D64">
+        <f>(Test2!C15-C15)/C15*100</f>
+        <v>1.4382632293080047</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C65">
+        <v>5</v>
+      </c>
+      <c r="D65">
+        <f>(Test2!C20-C20)/C20*100</f>
+        <v>4.3722673329169268</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C66">
+        <v>6</v>
+      </c>
+      <c r="D66">
+        <f>(Test2!C25-C25)/C25*100</f>
+        <v>4.9675023212627618</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C67">
+        <v>7</v>
+      </c>
+      <c r="D67">
+        <f>(Test2!C30-C30)/C30*100</f>
+        <v>4.6431642304385266</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68">
+        <f>(Test2!C35-C35)/C35*100</f>
+        <v>-3.1413612565445099</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C69">
+        <v>9</v>
+      </c>
+      <c r="D69">
+        <f>(Test2!C40-Test1!C40)/Test1!C40*100</f>
+        <v>-3.8311688311688346</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <f>(Test2!C45-Test1!C45)/Test1!C45*100</f>
+        <v>-11.686143572621036</v>
       </c>
     </row>
   </sheetData>
@@ -2150,36 +2247,36 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19" t="s">
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
@@ -2253,7 +2350,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2270,7 +2367,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -2288,7 +2385,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -2306,7 +2403,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="20"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -2324,7 +2421,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -2342,7 +2439,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="20" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2359,7 +2456,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="15"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -2380,7 +2477,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -2398,7 +2495,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="15"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -2416,7 +2513,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
+      <c r="A15" s="20"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -2505,7 +2602,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="25"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="8" t="s">
         <v>12</v>
       </c>
@@ -2523,7 +2620,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="24" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -2540,7 +2637,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
@@ -2558,7 +2655,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -2576,7 +2673,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="17"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -2594,7 +2691,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -2612,7 +2709,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="23" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2629,7 +2726,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
@@ -2650,7 +2747,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="17"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
@@ -2668,7 +2765,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -2686,7 +2783,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
+      <c r="A30" s="25"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
@@ -2704,7 +2801,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="26" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -2721,7 +2818,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
+      <c r="A32" s="27"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -2739,7 +2836,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
+      <c r="A33" s="27"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -2757,7 +2854,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
+      <c r="A34" s="27"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -2775,7 +2872,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
+      <c r="A35" s="28"/>
       <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
@@ -2793,7 +2890,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="26" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2810,7 +2907,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
+      <c r="A37" s="27"/>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
@@ -2831,7 +2928,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
+      <c r="A38" s="27"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -2849,7 +2946,7 @@
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
+      <c r="A39" s="27"/>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -2867,7 +2964,7 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="24"/>
+      <c r="A40" s="28"/>
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
@@ -2885,7 +2982,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="26" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -2902,7 +2999,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -2920,7 +3017,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
+      <c r="A43" s="27"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -2941,7 +3038,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
+      <c r="A44" s="27"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -2959,7 +3056,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A45" s="24"/>
+      <c r="A45" s="28"/>
       <c r="B45" s="1" t="s">
         <v>12</v>
       </c>
@@ -2977,7 +3074,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="23" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -3012,7 +3109,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A47" s="17"/>
+      <c r="A47" s="24"/>
       <c r="B47" s="1" t="s">
         <v>9</v>
       </c>
@@ -3078,7 +3175,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A48" s="17"/>
+      <c r="A48" s="24"/>
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
@@ -3120,7 +3217,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -3186,7 +3283,7 @@
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A50" s="18"/>
+      <c r="A50" s="25"/>
       <c r="B50" s="1" t="s">
         <v>12</v>
       </c>
@@ -3228,7 +3325,7 @@
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="23" t="s">
         <v>28</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -3263,7 +3360,7 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A52" s="17"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
@@ -3329,7 +3426,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A53" s="17"/>
+      <c r="A53" s="24"/>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
@@ -3371,7 +3468,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A54" s="17"/>
+      <c r="A54" s="24"/>
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -3437,7 +3534,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A55" s="18"/>
+      <c r="A55" s="25"/>
       <c r="B55" s="1" t="s">
         <v>12</v>
       </c>
@@ -3516,36 +3613,36 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19" t="s">
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
@@ -3708,7 +3805,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="20" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -3725,7 +3822,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="15"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -3743,7 +3840,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="15"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3761,7 +3858,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="15"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -3779,7 +3876,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
+      <c r="A15" s="20"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -3978,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -3995,7 +4092,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
@@ -4013,7 +4110,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="20"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
@@ -4031,7 +4128,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="20"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -4049,7 +4146,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="20"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
@@ -4067,7 +4164,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -4084,7 +4181,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
+      <c r="A32" s="20"/>
       <c r="B32" s="1" t="s">
         <v>9</v>
       </c>
@@ -4102,7 +4199,7 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A33" s="15"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
@@ -4120,7 +4217,7 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A34" s="15"/>
+      <c r="A34" s="20"/>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -4138,7 +4235,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
+      <c r="A35" s="20"/>
       <c r="B35" s="1" t="s">
         <v>12</v>
       </c>
@@ -4156,7 +4253,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="20" t="s">
         <v>20</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -4173,7 +4270,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
+      <c r="A37" s="20"/>
       <c r="B37" s="1" t="s">
         <v>9</v>
       </c>
@@ -4191,7 +4288,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
+      <c r="A38" s="20"/>
       <c r="B38" s="1" t="s">
         <v>10</v>
       </c>
@@ -4209,7 +4306,7 @@
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A39" s="15"/>
+      <c r="A39" s="20"/>
       <c r="B39" s="1" t="s">
         <v>11</v>
       </c>
@@ -4227,7 +4324,7 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
+      <c r="A40" s="20"/>
       <c r="B40" s="1" t="s">
         <v>12</v>
       </c>
@@ -4245,7 +4342,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="20" t="s">
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -4262,7 +4359,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A42" s="15"/>
+      <c r="A42" s="20"/>
       <c r="B42" s="1" t="s">
         <v>9</v>
       </c>
@@ -4280,7 +4377,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
+      <c r="A43" s="20"/>
       <c r="B43" s="1" t="s">
         <v>10</v>
       </c>
@@ -4298,7 +4395,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A44" s="15"/>
+      <c r="A44" s="20"/>
       <c r="B44" s="1" t="s">
         <v>11</v>
       </c>
@@ -4316,7 +4413,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
+      <c r="A45" s="20"/>
       <c r="B45" s="1" t="s">
         <v>12</v>
       </c>
@@ -4334,7 +4431,7 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="19" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -4369,7 +4466,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
+      <c r="A47" s="19"/>
       <c r="B47" s="14" t="s">
         <v>9</v>
       </c>
@@ -4435,7 +4532,7 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
+      <c r="A48" s="19"/>
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
@@ -4477,7 +4574,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A49" s="20"/>
+      <c r="A49" s="19"/>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
@@ -4543,7 +4640,7 @@
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="19" t="s">
         <v>28</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -4587,7 +4684,7 @@
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A51" s="20"/>
+      <c r="A51" s="19"/>
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
@@ -4620,7 +4717,7 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A52" s="20"/>
+      <c r="A52" s="19"/>
       <c r="B52" s="14" t="s">
         <v>9</v>
       </c>
@@ -4686,7 +4783,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A53" s="20"/>
+      <c r="A53" s="19"/>
       <c r="B53" s="1" t="s">
         <v>10</v>
       </c>
@@ -4835,11 +4932,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A36:A40"/>
     <mergeCell ref="A41:A45"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="A50:A53"/>
@@ -4850,6 +4942,11 @@
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="A21:A25"/>
     <mergeCell ref="A26:A30"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A36:A40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4857,7 +4954,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986CE34A-0472-4CC3-8683-488EBE5AEA7F}">
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
@@ -4871,36 +4968,36 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B3" s="1"/>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19" t="s">
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19" t="s">
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B4" s="1"/>
@@ -4974,7 +5071,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="20" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -5009,7 +5106,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
+      <c r="A7" s="20"/>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
@@ -5075,7 +5172,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="15"/>
+      <c r="A8" s="20"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -5117,7 +5214,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -5183,7 +5280,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="15"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -5225,7 +5322,7 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -5260,7 +5357,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -5326,7 +5423,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -5368,7 +5465,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -5434,7 +5531,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -5476,7 +5573,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -5511,7 +5608,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="1" t="s">
         <v>9</v>
       </c>
@@ -5577,7 +5674,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -5619,7 +5716,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
+      <c r="A19" s="20"/>
       <c r="B19" s="1" t="s">
         <v>11</v>
       </c>
@@ -5685,7 +5782,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A20" s="15"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="1" t="s">
         <v>12</v>
       </c>
@@ -5727,7 +5824,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="20" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -5762,7 +5859,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
@@ -5828,7 +5925,7 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
@@ -5861,7 +5958,7 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
@@ -5927,7 +6024,7 @@
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
@@ -5968,17 +6065,59 @@
         <v>99.886779801835075</v>
       </c>
     </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <f>(C10-C8)/C8*100</f>
+        <v>13.682112605879418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <f>(C15-C13)/C13*100</f>
+        <v>13.045084996304491</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <f>(C20-C18)/C18*100</f>
+        <v>11.408573928258976</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <f>(C25-C23)/C23*100</f>
+        <v>9.5200000000000014</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C33">
+        <f>AVERAGE(C29:C32)</f>
+        <v>11.913942882610721</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:N3"/>
     <mergeCell ref="O3:R3"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A16:A20"/>
-    <mergeCell ref="A21:A25"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
